--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="340" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{740A0C33-755D-4649-928B-F7B2EAD49CFC}"/>
+  <xr:revisionPtr revIDLastSave="352" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B84671FD-AB47-46D9-BEEA-B2715FFBB604}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Retos" sheetId="4" r:id="rId1"/>
@@ -7429,12 +7429,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7444,6 +7438,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -15209,7 +15209,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L288" xr:uid="{D5CC9271-A20F-4DAE-A693-53F4455B4AEF}"/>
   <conditionalFormatting sqref="K16">
     <cfRule type="duplicateValues" dxfId="27" priority="6"/>
   </conditionalFormatting>
@@ -16696,15 +16695,15 @@
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
       <c r="Q1"/>
-      <c r="R1" s="144" t="s">
+      <c r="R1" s="142" t="s">
         <v>175</v>
       </c>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="145"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
+      <c r="S1" s="143"/>
+      <c r="T1" s="143"/>
+      <c r="U1" s="143"/>
+      <c r="V1" s="143"/>
+      <c r="W1" s="143"/>
+      <c r="X1" s="143"/>
     </row>
     <row r="2" spans="1:24" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -17517,19 +17516,19 @@
       <c r="M15" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="N15" s="140"/>
-      <c r="O15" s="140"/>
-      <c r="P15" s="142" t="s">
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="140" t="s">
         <v>264</v>
       </c>
-      <c r="Q15" s="142"/>
-      <c r="R15" s="142"/>
-      <c r="S15" s="142"/>
-      <c r="T15" s="142"/>
-      <c r="U15" s="142"/>
-      <c r="V15" s="142"/>
-      <c r="W15" s="142"/>
-      <c r="X15" s="142"/>
+      <c r="Q15" s="140"/>
+      <c r="R15" s="140"/>
+      <c r="S15" s="140"/>
+      <c r="T15" s="140"/>
+      <c r="U15" s="140"/>
+      <c r="V15" s="140"/>
+      <c r="W15" s="140"/>
+      <c r="X15" s="140"/>
     </row>
     <row r="16" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
@@ -17571,17 +17570,17 @@
       <c r="M16" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="N16" s="141"/>
-      <c r="O16" s="141"/>
-      <c r="P16" s="143"/>
-      <c r="Q16" s="143"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="143"/>
-      <c r="T16" s="143"/>
-      <c r="U16" s="143"/>
-      <c r="V16" s="143"/>
-      <c r="W16" s="143"/>
-      <c r="X16" s="143"/>
+      <c r="N16" s="145"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="141"/>
+      <c r="Q16" s="141"/>
+      <c r="R16" s="141"/>
+      <c r="S16" s="141"/>
+      <c r="T16" s="141"/>
+      <c r="U16" s="141"/>
+      <c r="V16" s="141"/>
+      <c r="W16" s="141"/>
+      <c r="X16" s="141"/>
     </row>
     <row r="17" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
@@ -21124,6 +21123,11 @@
   </sheetData>
   <autoFilter ref="A2:X2" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}"/>
   <mergeCells count="12">
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
     <mergeCell ref="V15:V16"/>
     <mergeCell ref="W15:W16"/>
     <mergeCell ref="X15:X16"/>
@@ -21131,11 +21135,6 @@
     <mergeCell ref="S15:S16"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="U15:U16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21144,6 +21143,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{980A29CF-D105-47BF-A299-22EED3F87C99}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -21203,7 +21203,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="129" t="s">
         <v>588</v>
       </c>
@@ -21254,7 +21254,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="129" t="s">
         <v>596</v>
       </c>
@@ -21305,7 +21305,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="129" t="s">
         <v>596</v>
       </c>
@@ -21354,7 +21354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="129" t="s">
         <v>564</v>
       </c>
@@ -21403,7 +21403,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="403.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="129" t="s">
         <v>564</v>
       </c>
@@ -21449,7 +21449,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>577</v>
       </c>
@@ -21497,7 +21497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="129" t="s">
         <v>560</v>
       </c>
@@ -21544,7 +21544,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="129" t="s">
         <v>607</v>
       </c>
@@ -21587,7 +21587,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>607</v>
       </c>
@@ -21632,7 +21632,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="129" t="s">
         <v>562</v>
       </c>
@@ -21679,7 +21679,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="129" t="s">
         <v>562</v>
       </c>
@@ -21724,7 +21724,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>562</v>
       </c>
@@ -21771,7 +21771,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="129" t="s">
         <v>588</v>
       </c>
@@ -21816,7 +21816,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="129" t="s">
         <v>588</v>
       </c>
@@ -21859,7 +21859,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="129" t="s">
         <v>562</v>
       </c>
@@ -21902,7 +21902,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="129" t="s">
         <v>577</v>
       </c>
@@ -21947,7 +21947,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="129" t="s">
         <v>596</v>
       </c>
@@ -21974,7 +21974,7 @@
       <c r="N18" s="126"/>
       <c r="O18" s="126"/>
     </row>
-    <row r="19" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="129" t="s">
         <v>596</v>
       </c>
@@ -22019,7 +22019,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="129" t="s">
         <v>577</v>
       </c>
@@ -22064,7 +22064,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="129" t="s">
         <v>588</v>
       </c>
@@ -22095,7 +22095,7 @@
       <c r="N21" s="126"/>
       <c r="O21" s="126"/>
     </row>
-    <row r="22" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>607</v>
       </c>
@@ -22185,7 +22185,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="129" t="s">
         <v>568</v>
       </c>
@@ -22230,7 +22230,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="129" t="s">
         <v>568</v>
       </c>
@@ -22273,7 +22273,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>568</v>
       </c>
@@ -22316,7 +22316,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="129" t="s">
         <v>590</v>
       </c>
@@ -22363,7 +22363,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="129" t="s">
         <v>590</v>
       </c>
@@ -22409,6 +22409,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q28" xr:uid="{980A29CF-D105-47BF-A299-22EED3F87C99}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="REGISTRO Y CONTROL"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="B7">
     <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
@@ -22430,7 +22437,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5292D3F-0B6E-46E3-A044-1C46EB00664B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -22454,7 +22460,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>542</v>
       </c>
@@ -22468,7 +22474,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="115" t="s">
         <v>545</v>
       </c>
@@ -22482,7 +22488,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>548</v>
       </c>
@@ -22496,7 +22502,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>550</v>
       </c>
@@ -22510,7 +22516,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>545</v>
       </c>
@@ -22524,7 +22530,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>542</v>
       </c>
@@ -22538,7 +22544,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>550</v>
       </c>
@@ -22552,7 +22558,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>559</v>
       </c>
@@ -22566,7 +22572,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>559</v>
       </c>
@@ -22580,7 +22586,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>559</v>
       </c>
@@ -22594,7 +22600,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>559</v>
       </c>
@@ -22608,7 +22614,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>559</v>
       </c>
@@ -22622,7 +22628,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="115" t="s">
         <v>548</v>
       </c>
@@ -22636,7 +22642,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>542</v>
       </c>
@@ -22650,7 +22656,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>550</v>
       </c>
@@ -22664,7 +22670,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>550</v>
       </c>
@@ -22678,7 +22684,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>550</v>
       </c>
@@ -22692,7 +22698,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="115" t="s">
         <v>548</v>
       </c>
@@ -22706,7 +22712,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="115" t="s">
         <v>548</v>
       </c>
@@ -22720,7 +22726,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>559</v>
       </c>
@@ -22734,7 +22740,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>550</v>
       </c>
@@ -22748,7 +22754,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>550</v>
       </c>
@@ -22776,7 +22782,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="115" t="s">
         <v>582</v>
       </c>
@@ -22790,7 +22796,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>559</v>
       </c>
@@ -22804,7 +22810,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>559</v>
       </c>
@@ -22818,7 +22824,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>548</v>
       </c>
@@ -22832,7 +22838,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>559</v>
       </c>
@@ -22846,7 +22852,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>548</v>
       </c>
@@ -22860,7 +22866,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>550</v>
       </c>
@@ -22874,7 +22880,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>542</v>
       </c>
@@ -22888,7 +22894,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>548</v>
       </c>
@@ -22902,7 +22908,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>559</v>
       </c>
@@ -22916,7 +22922,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>559</v>
       </c>
@@ -22930,7 +22936,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>559</v>
       </c>
@@ -22944,7 +22950,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>542</v>
       </c>
@@ -22958,7 +22964,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="115" t="s">
         <v>548</v>
       </c>
@@ -22972,7 +22978,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>542</v>
       </c>
@@ -22986,7 +22992,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>559</v>
       </c>
@@ -23000,7 +23006,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>548</v>
       </c>
@@ -23014,7 +23020,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>548</v>
       </c>
@@ -23028,7 +23034,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>548</v>
       </c>
@@ -23042,7 +23048,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="115" t="s">
         <v>606</v>
       </c>
@@ -23056,7 +23062,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>559</v>
       </c>
@@ -23070,7 +23076,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="115" t="s">
         <v>545</v>
       </c>
@@ -23084,7 +23090,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>559</v>
       </c>
@@ -23098,7 +23104,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>559</v>
       </c>
@@ -23112,7 +23118,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="115" t="s">
         <v>606</v>
       </c>
@@ -23126,7 +23132,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="115" t="s">
         <v>606</v>
       </c>
@@ -23140,7 +23146,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="115" t="s">
         <v>545</v>
       </c>
@@ -23154,7 +23160,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="115" t="s">
         <v>559</v>
       </c>
@@ -23168,7 +23174,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="115" t="s">
         <v>582</v>
       </c>
@@ -23183,13 +23189,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D53" xr:uid="{D5292D3F-0B6E-46E3-A044-1C46EB00664B}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Rematrícula"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D53" xr:uid="{D5292D3F-0B6E-46E3-A044-1C46EB00664B}"/>
   <conditionalFormatting sqref="B3">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>

--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="352" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B84671FD-AB47-46D9-BEEA-B2715FFBB604}"/>
+  <xr:revisionPtr revIDLastSave="365" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9628E8FB-D2D7-4A44-B2FD-D6341B2F0DE0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Retos" sheetId="4" r:id="rId1"/>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4213" uniqueCount="1527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4213" uniqueCount="1524">
   <si>
     <t>Nombre del Proyecto</t>
   </si>
@@ -4108,9 +4108,6 @@
   </si>
   <si>
     <t>Estado de la propuesta de indicadores</t>
-  </si>
-  <si>
-    <t>GESTIÓN DOCENTE</t>
   </si>
   <si>
     <t>Garantizar la gestión integral de la docencia en el POLI, de los diferentes niveles de formación y modalidades.</t>
@@ -5269,9 +5266,6 @@
     <t>Diseñar, implementar y evaluar experiencias inmersivas e innovadoras que fortalezcan los procesos educativos, promuevan la adquisición de competencias específicas y faciliten el logro de los resultados de aprendizaje, mediante el uso de tecnologías educativas alineadas con los objetivos curriculares.</t>
   </si>
   <si>
-    <t>OPERACIONES ACADÉMICAS</t>
-  </si>
-  <si>
     <t>Asegurar una operación académica de calidad en los diferentes niveles y modalidades en educación formal, a través de la gestión oportuna de los procesos que nos
 permite contribuir en su objetivo profesional y de vida.</t>
   </si>
@@ -5347,9 +5341,6 @@
   </si>
   <si>
     <t>Gestionar, monitorear y mejorar continuamente la operación académica en los diferentes niveles y modalidades de educación formal, garantizando la calidad, oportunidad y eficiencia de los procesos, en apoyo al logro de los objetivos académicos y profesionales de los estudiantes.</t>
-  </si>
-  <si>
-    <t>OPERACIÓN DE EDUCACIÓN NO FORMAL</t>
   </si>
   <si>
     <t>OBJETIVO Asegurar la operación de los proyectos de Educación para la Vida, respondiendo a los requerimientos de los clientes y estudiantes con calidad, oportunidad y satisfacción.</t>
@@ -5832,9 +5823,6 @@
     <t>Nivel de satisfacción de docentes y estudiantes con los contenidos virtuales</t>
   </si>
   <si>
-    <t>GESTIÓN DE UNIDADES ACADÉMICAS</t>
-  </si>
-  <si>
     <t>Gestionar y acompañar los planes de estudio de los programas académicos en correspondencia con las políticas, reglamentos y estrategias institucionales para promover la
 formación integral del estudiante.</t>
   </si>
@@ -6519,6 +6507,9 @@
   </si>
   <si>
     <t>Subroceso</t>
+  </si>
+  <si>
+    <t>OPERACIÓN DE NUEVOS NEGOCIOS Y CI</t>
   </si>
 </sst>
 </file>
@@ -7429,6 +7420,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7438,12 +7435,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -15209,6 +15200,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L288" xr:uid="{D5CC9271-A20F-4DAE-A693-53F4455B4AEF}"/>
   <conditionalFormatting sqref="K16">
     <cfRule type="duplicateValues" dxfId="27" priority="6"/>
   </conditionalFormatting>
@@ -16695,15 +16687,15 @@
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
       <c r="Q1"/>
-      <c r="R1" s="142" t="s">
+      <c r="R1" s="144" t="s">
         <v>175</v>
       </c>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
     </row>
     <row r="2" spans="1:24" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -17516,19 +17508,19 @@
       <c r="M15" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="N15" s="144"/>
-      <c r="O15" s="144"/>
-      <c r="P15" s="140" t="s">
+      <c r="N15" s="140"/>
+      <c r="O15" s="140"/>
+      <c r="P15" s="142" t="s">
         <v>264</v>
       </c>
-      <c r="Q15" s="140"/>
-      <c r="R15" s="140"/>
-      <c r="S15" s="140"/>
-      <c r="T15" s="140"/>
-      <c r="U15" s="140"/>
-      <c r="V15" s="140"/>
-      <c r="W15" s="140"/>
-      <c r="X15" s="140"/>
+      <c r="Q15" s="142"/>
+      <c r="R15" s="142"/>
+      <c r="S15" s="142"/>
+      <c r="T15" s="142"/>
+      <c r="U15" s="142"/>
+      <c r="V15" s="142"/>
+      <c r="W15" s="142"/>
+      <c r="X15" s="142"/>
     </row>
     <row r="16" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
@@ -17570,17 +17562,17 @@
       <c r="M16" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="N16" s="145"/>
-      <c r="O16" s="145"/>
-      <c r="P16" s="141"/>
-      <c r="Q16" s="141"/>
-      <c r="R16" s="141"/>
-      <c r="S16" s="141"/>
-      <c r="T16" s="141"/>
-      <c r="U16" s="141"/>
-      <c r="V16" s="141"/>
-      <c r="W16" s="141"/>
-      <c r="X16" s="141"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="141"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="143"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="143"/>
+      <c r="T16" s="143"/>
+      <c r="U16" s="143"/>
+      <c r="V16" s="143"/>
+      <c r="W16" s="143"/>
+      <c r="X16" s="143"/>
     </row>
     <row r="17" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
@@ -21123,11 +21115,6 @@
   </sheetData>
   <autoFilter ref="A2:X2" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}"/>
   <mergeCells count="12">
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
     <mergeCell ref="V15:V16"/>
     <mergeCell ref="W15:W16"/>
     <mergeCell ref="X15:X16"/>
@@ -21135,6 +21122,11 @@
     <mergeCell ref="S15:S16"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="U15:U16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21143,7 +21135,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{980A29CF-D105-47BF-A299-22EED3F87C99}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -21155,7 +21146,7 @@
         <v>173</v>
       </c>
       <c r="B1" s="125" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="C1" s="125" t="s">
         <v>1242</v>
@@ -21203,49 +21194,49 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="129" t="s">
         <v>588</v>
       </c>
       <c r="B2" s="129" t="s">
+        <v>589</v>
+      </c>
+      <c r="C2" s="130" t="s">
         <v>1257</v>
       </c>
-      <c r="C2" s="130" t="s">
+      <c r="D2" s="126" t="s">
         <v>1258</v>
       </c>
-      <c r="D2" s="126" t="s">
+      <c r="E2" s="126" t="s">
         <v>1259</v>
       </c>
-      <c r="E2" s="126" t="s">
+      <c r="F2" s="126" t="s">
         <v>1260</v>
-      </c>
-      <c r="F2" s="126" t="s">
-        <v>1261</v>
       </c>
       <c r="G2" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H2" s="126" t="s">
+        <v>1261</v>
+      </c>
+      <c r="I2" s="126" t="s">
         <v>1262</v>
-      </c>
-      <c r="I2" s="126" t="s">
-        <v>1263</v>
       </c>
       <c r="J2" s="126"/>
       <c r="K2" s="126" t="s">
+        <v>1263</v>
+      </c>
+      <c r="L2" s="126" t="s">
         <v>1264</v>
       </c>
-      <c r="L2" s="126" t="s">
+      <c r="M2" s="126" t="s">
         <v>1265</v>
       </c>
-      <c r="M2" s="126" t="s">
+      <c r="N2" s="126" t="s">
         <v>1266</v>
       </c>
-      <c r="N2" s="126" t="s">
+      <c r="O2" s="126" t="s">
         <v>1267</v>
-      </c>
-      <c r="O2" s="126" t="s">
-        <v>1268</v>
       </c>
       <c r="P2" s="124" t="s">
         <v>8</v>
@@ -21254,46 +21245,46 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="129" t="s">
         <v>596</v>
       </c>
       <c r="B3" s="126" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C3" s="129" t="s">
         <v>1269</v>
       </c>
-      <c r="C3" s="129" t="s">
+      <c r="D3" s="126" t="s">
         <v>1270</v>
       </c>
-      <c r="D3" s="126" t="s">
+      <c r="E3" s="126" t="s">
         <v>1271</v>
       </c>
-      <c r="E3" s="126" t="s">
+      <c r="F3" s="126" t="s">
         <v>1272</v>
-      </c>
-      <c r="F3" s="126" t="s">
-        <v>1273</v>
       </c>
       <c r="G3" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H3" s="126" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I3" s="126" t="s">
+        <v>1273</v>
+      </c>
+      <c r="J3" s="126" t="s">
         <v>1274</v>
       </c>
-      <c r="I3" s="126" t="s">
-        <v>1274</v>
-      </c>
-      <c r="J3" s="126" t="s">
+      <c r="K3" s="126" t="s">
         <v>1275</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="L3" s="126" t="s">
         <v>1276</v>
-      </c>
-      <c r="L3" s="126" t="s">
-        <v>1277</v>
       </c>
       <c r="M3" s="126"/>
       <c r="N3" s="126" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="O3" s="126" t="s">
         <v>404</v>
@@ -21302,50 +21293,50 @@
         <v>8</v>
       </c>
       <c r="Q3" s="124" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="129" t="s">
         <v>596</v>
       </c>
       <c r="B4" s="126" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C4" s="126" t="s">
         <v>1280</v>
       </c>
-      <c r="C4" s="126" t="s">
+      <c r="D4" s="126" t="s">
         <v>1281</v>
       </c>
-      <c r="D4" s="126" t="s">
+      <c r="E4" s="126" t="s">
         <v>1282</v>
       </c>
-      <c r="E4" s="126" t="s">
+      <c r="F4" s="126" t="s">
         <v>1283</v>
-      </c>
-      <c r="F4" s="126" t="s">
-        <v>1284</v>
       </c>
       <c r="G4" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H4" s="126" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="I4" s="126"/>
       <c r="J4" s="126"/>
       <c r="K4" s="133" t="s">
+        <v>1285</v>
+      </c>
+      <c r="L4" s="134" t="s">
         <v>1286</v>
       </c>
-      <c r="L4" s="134" t="s">
+      <c r="M4" s="134" t="s">
         <v>1287</v>
       </c>
-      <c r="M4" s="134" t="s">
+      <c r="N4" s="135" t="s">
         <v>1288</v>
       </c>
-      <c r="N4" s="135" t="s">
+      <c r="O4" s="134" t="s">
         <v>1289</v>
-      </c>
-      <c r="O4" s="134" t="s">
-        <v>1290</v>
       </c>
       <c r="P4" s="124" t="s">
         <v>8</v>
@@ -21354,7 +21345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="129" t="s">
         <v>564</v>
       </c>
@@ -21362,94 +21353,94 @@
         <v>565</v>
       </c>
       <c r="C5" s="126" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D5" s="126" t="s">
         <v>1291</v>
       </c>
-      <c r="D5" s="126" t="s">
+      <c r="E5" s="126" t="s">
         <v>1292</v>
       </c>
-      <c r="E5" s="126" t="s">
+      <c r="F5" s="126" t="s">
         <v>1293</v>
-      </c>
-      <c r="F5" s="126" t="s">
-        <v>1294</v>
       </c>
       <c r="G5" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H5" s="126" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="I5" s="126"/>
       <c r="J5" s="126"/>
       <c r="K5" s="126" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L5" s="126" t="s">
         <v>1296</v>
-      </c>
-      <c r="L5" s="126" t="s">
-        <v>1297</v>
       </c>
       <c r="M5" s="126" t="s">
         <v>404</v>
       </c>
       <c r="N5" s="137" t="s">
+        <v>1297</v>
+      </c>
+      <c r="O5" s="126" t="s">
         <v>1298</v>
       </c>
-      <c r="O5" s="126" t="s">
-        <v>1299</v>
-      </c>
       <c r="P5" s="124" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q5" s="124" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="403.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A6" s="129" t="s">
         <v>564</v>
       </c>
       <c r="B6" s="126" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C6" s="126" t="s">
         <v>1300</v>
       </c>
-      <c r="C6" s="126" t="s">
+      <c r="D6" s="126" t="s">
         <v>1301</v>
       </c>
-      <c r="D6" s="126" t="s">
+      <c r="E6" s="126" t="s">
         <v>1302</v>
       </c>
-      <c r="E6" s="126" t="s">
+      <c r="F6" s="126" t="s">
         <v>1303</v>
-      </c>
-      <c r="F6" s="126" t="s">
-        <v>1304</v>
       </c>
       <c r="G6" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H6" s="126" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="I6" s="126"/>
       <c r="J6" s="126"/>
       <c r="K6" s="126" t="s">
+        <v>1305</v>
+      </c>
+      <c r="L6" s="126" t="s">
         <v>1306</v>
       </c>
-      <c r="L6" s="126" t="s">
+      <c r="M6" s="126" t="s">
         <v>1307</v>
-      </c>
-      <c r="M6" s="126" t="s">
-        <v>1308</v>
       </c>
       <c r="N6" s="136" t="s">
         <v>404</v>
       </c>
       <c r="O6" s="126" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="P6" s="124" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>577</v>
       </c>
@@ -21457,47 +21448,47 @@
         <v>578</v>
       </c>
       <c r="C7" s="126" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D7" s="126" t="s">
         <v>1310</v>
       </c>
-      <c r="D7" s="126" t="s">
+      <c r="E7" s="126" t="s">
         <v>1311</v>
       </c>
-      <c r="E7" s="126" t="s">
+      <c r="F7" s="126" t="s">
         <v>1312</v>
-      </c>
-      <c r="F7" s="126" t="s">
-        <v>1313</v>
       </c>
       <c r="G7" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H7" s="126" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I7" s="126" t="s">
         <v>1314</v>
-      </c>
-      <c r="I7" s="126" t="s">
-        <v>1315</v>
       </c>
       <c r="J7" s="126"/>
       <c r="K7" s="126" t="s">
+        <v>1315</v>
+      </c>
+      <c r="L7" s="126" t="s">
         <v>1316</v>
       </c>
-      <c r="L7" s="126" t="s">
+      <c r="M7" s="126" t="s">
         <v>1317</v>
       </c>
-      <c r="M7" s="126" t="s">
+      <c r="N7" s="126" t="s">
         <v>1318</v>
       </c>
-      <c r="N7" s="126" t="s">
+      <c r="O7" s="126" t="s">
         <v>1319</v>
-      </c>
-      <c r="O7" s="126" t="s">
-        <v>1320</v>
       </c>
       <c r="P7" s="124" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="129" t="s">
         <v>560</v>
       </c>
@@ -21505,77 +21496,77 @@
         <v>560</v>
       </c>
       <c r="C8" s="138" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D8" s="126" t="s">
         <v>1321</v>
       </c>
-      <c r="D8" s="126" t="s">
+      <c r="E8" s="126" t="s">
         <v>1322</v>
       </c>
-      <c r="E8" s="126" t="s">
+      <c r="F8" s="126" t="s">
         <v>1323</v>
-      </c>
-      <c r="F8" s="126" t="s">
-        <v>1324</v>
       </c>
       <c r="G8" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H8" s="126" t="s">
+        <v>1324</v>
+      </c>
+      <c r="I8" s="126" t="s">
         <v>1325</v>
       </c>
-      <c r="I8" s="126" t="s">
+      <c r="J8" s="126" t="s">
         <v>1326</v>
       </c>
-      <c r="J8" s="126" t="s">
+      <c r="K8" s="126" t="s">
         <v>1327</v>
-      </c>
-      <c r="K8" s="126" t="s">
-        <v>1328</v>
       </c>
       <c r="L8" s="126" t="s">
         <v>404</v>
       </c>
       <c r="M8" s="126" t="s">
+        <v>1328</v>
+      </c>
+      <c r="N8" s="126" t="s">
         <v>1329</v>
       </c>
-      <c r="N8" s="126" t="s">
+      <c r="O8" s="126" t="s">
         <v>1330</v>
       </c>
-      <c r="O8" s="126" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="129" t="s">
         <v>607</v>
       </c>
       <c r="B9" s="131" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C9" s="131" t="s">
         <v>1332</v>
       </c>
-      <c r="C9" s="131" t="s">
+      <c r="D9" s="131" t="s">
         <v>1333</v>
       </c>
-      <c r="D9" s="131" t="s">
+      <c r="E9" s="131" t="s">
         <v>1334</v>
       </c>
-      <c r="E9" s="131" t="s">
+      <c r="F9" s="131" t="s">
         <v>1335</v>
-      </c>
-      <c r="F9" s="131" t="s">
-        <v>1336</v>
       </c>
       <c r="G9" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H9" s="126" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="I9" s="126"/>
       <c r="J9" s="126"/>
       <c r="K9" s="126" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L9" s="126" t="s">
         <v>1338</v>
-      </c>
-      <c r="L9" s="126" t="s">
-        <v>1339</v>
       </c>
       <c r="M9" s="126" t="s">
         <v>404</v>
@@ -21584,10 +21575,10 @@
         <v>404</v>
       </c>
       <c r="O9" s="126" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>607</v>
       </c>
@@ -21595,136 +21586,136 @@
         <v>615</v>
       </c>
       <c r="C10" s="130" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D10" s="131" t="s">
         <v>1341</v>
       </c>
-      <c r="D10" s="131" t="s">
+      <c r="E10" s="131" t="s">
         <v>1342</v>
       </c>
-      <c r="E10" s="131" t="s">
+      <c r="F10" s="131" t="s">
         <v>1343</v>
-      </c>
-      <c r="F10" s="131" t="s">
-        <v>1344</v>
       </c>
       <c r="G10" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H10" s="126" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I10" s="126"/>
       <c r="J10" s="126" t="s">
+        <v>1345</v>
+      </c>
+      <c r="K10" s="126" t="s">
         <v>1346</v>
       </c>
-      <c r="K10" s="126" t="s">
+      <c r="L10" s="126" t="s">
         <v>1347</v>
       </c>
-      <c r="L10" s="126" t="s">
+      <c r="M10" s="126" t="s">
         <v>1348</v>
       </c>
-      <c r="M10" s="126" t="s">
+      <c r="N10" s="126" t="s">
         <v>1349</v>
       </c>
-      <c r="N10" s="126" t="s">
+      <c r="O10" s="126" t="s">
         <v>1350</v>
       </c>
-      <c r="O10" s="126" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="129" t="s">
         <v>562</v>
       </c>
       <c r="B11" s="136" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C11" s="136" t="s">
         <v>1352</v>
       </c>
-      <c r="C11" s="136" t="s">
+      <c r="D11" s="136" t="s">
         <v>1353</v>
       </c>
-      <c r="D11" s="136" t="s">
+      <c r="E11" s="136" t="s">
         <v>1354</v>
       </c>
-      <c r="E11" s="136" t="s">
+      <c r="F11" s="136" t="s">
         <v>1355</v>
-      </c>
-      <c r="F11" s="136" t="s">
-        <v>1356</v>
       </c>
       <c r="G11" s="136" t="s">
         <v>561</v>
       </c>
       <c r="H11" s="139" t="s">
+        <v>1356</v>
+      </c>
+      <c r="I11" s="136" t="s">
         <v>1357</v>
       </c>
-      <c r="I11" s="136" t="s">
+      <c r="J11" s="136" t="s">
         <v>1358</v>
       </c>
-      <c r="J11" s="136" t="s">
+      <c r="K11" s="136" t="s">
         <v>1359</v>
       </c>
-      <c r="K11" s="136" t="s">
+      <c r="L11" s="139" t="s">
         <v>1360</v>
-      </c>
-      <c r="L11" s="139" t="s">
-        <v>1361</v>
       </c>
       <c r="M11" s="136" t="s">
         <v>404</v>
       </c>
       <c r="N11" s="139" t="s">
+        <v>1361</v>
+      </c>
+      <c r="O11" s="136" t="s">
         <v>1362</v>
       </c>
-      <c r="O11" s="136" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12" s="129" t="s">
         <v>562</v>
       </c>
       <c r="B12" s="126" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C12" s="126" t="s">
         <v>1364</v>
       </c>
-      <c r="C12" s="126" t="s">
+      <c r="D12" s="126" t="s">
         <v>1365</v>
       </c>
-      <c r="D12" s="126" t="s">
+      <c r="E12" s="126" t="s">
         <v>1366</v>
       </c>
-      <c r="E12" s="126" t="s">
+      <c r="F12" s="126" t="s">
         <v>1367</v>
-      </c>
-      <c r="F12" s="126" t="s">
-        <v>1368</v>
       </c>
       <c r="G12" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H12" s="129" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="I12" s="126"/>
       <c r="J12" s="126" t="s">
+        <v>1369</v>
+      </c>
+      <c r="K12" s="129" t="s">
         <v>1370</v>
       </c>
-      <c r="K12" s="129" t="s">
+      <c r="L12" s="126" t="s">
         <v>1371</v>
-      </c>
-      <c r="L12" s="126" t="s">
-        <v>1372</v>
       </c>
       <c r="M12" s="126" t="s">
         <v>404</v>
       </c>
       <c r="N12" s="126" t="s">
+        <v>1372</v>
+      </c>
+      <c r="O12" s="126" t="s">
         <v>1373</v>
       </c>
-      <c r="O12" s="126" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>562</v>
       </c>
@@ -21732,76 +21723,76 @@
         <v>613</v>
       </c>
       <c r="C13" s="126" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D13" s="126" t="s">
         <v>1375</v>
       </c>
-      <c r="D13" s="126" t="s">
+      <c r="E13" s="126" t="s">
         <v>1376</v>
       </c>
-      <c r="E13" s="126" t="s">
+      <c r="F13" s="126" t="s">
         <v>1377</v>
-      </c>
-      <c r="F13" s="126" t="s">
-        <v>1378</v>
       </c>
       <c r="G13" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H13" s="126" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I13" s="126" t="s">
         <v>1379</v>
       </c>
-      <c r="I13" s="126" t="s">
+      <c r="J13" s="126" t="s">
         <v>1380</v>
       </c>
-      <c r="J13" s="126" t="s">
+      <c r="K13" s="126" t="s">
         <v>1381</v>
       </c>
-      <c r="K13" s="126" t="s">
+      <c r="L13" s="126" t="s">
         <v>1382</v>
-      </c>
-      <c r="L13" s="126" t="s">
-        <v>1383</v>
       </c>
       <c r="M13" s="126" t="s">
         <v>404</v>
       </c>
       <c r="N13" s="126" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="O13" s="126" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A14" s="129" t="s">
         <v>588</v>
       </c>
       <c r="B14" s="126" t="s">
+        <v>604</v>
+      </c>
+      <c r="C14" s="126" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D14" s="126" t="s">
         <v>1385</v>
       </c>
-      <c r="C14" s="126" t="s">
+      <c r="E14" s="126" t="s">
         <v>1386</v>
       </c>
-      <c r="D14" s="126" t="s">
+      <c r="F14" s="126" t="s">
         <v>1387</v>
-      </c>
-      <c r="E14" s="126" t="s">
-        <v>1388</v>
-      </c>
-      <c r="F14" s="126" t="s">
-        <v>1389</v>
       </c>
       <c r="G14" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H14" s="126" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="I14" s="126" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="J14" s="126"/>
       <c r="K14" s="126" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="L14" s="126" t="s">
         <v>404</v>
@@ -21810,149 +21801,149 @@
         <v>404</v>
       </c>
       <c r="N14" s="126" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="O14" s="126" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A15" s="129" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="B15" s="126" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C15" s="126" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D15" s="126" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E15" s="126" t="s">
         <v>1394</v>
       </c>
-      <c r="C15" s="126" t="s">
+      <c r="F15" s="126" t="s">
         <v>1395</v>
-      </c>
-      <c r="D15" s="126" t="s">
-        <v>1396</v>
-      </c>
-      <c r="E15" s="126" t="s">
-        <v>1397</v>
-      </c>
-      <c r="F15" s="126" t="s">
-        <v>1398</v>
       </c>
       <c r="G15" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H15" s="126" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="I15" s="126"/>
       <c r="J15" s="126"/>
       <c r="K15" s="126" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="L15" s="126" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="M15" s="126" t="s">
         <v>404</v>
       </c>
       <c r="N15" s="126" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="O15" s="126" t="s">
-        <v>1403</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A16" s="129" t="s">
         <v>562</v>
       </c>
       <c r="B16" s="126" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C16" s="126" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D16" s="126" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E16" s="126" t="s">
         <v>1404</v>
       </c>
-      <c r="C16" s="126" t="s">
+      <c r="F16" s="126" t="s">
         <v>1405</v>
-      </c>
-      <c r="D16" s="126" t="s">
-        <v>1406</v>
-      </c>
-      <c r="E16" s="126" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F16" s="126" t="s">
-        <v>1408</v>
       </c>
       <c r="G16" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H16" s="126" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="I16" s="126"/>
       <c r="J16" s="126"/>
       <c r="K16" s="126" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="L16" s="126" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="M16" s="126" t="s">
         <v>404</v>
       </c>
       <c r="N16" s="126" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="O16" s="126" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A17" s="129" t="s">
         <v>577</v>
       </c>
       <c r="B17" s="126" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C17" s="126" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D17" s="126" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E17" s="126" t="s">
         <v>1413</v>
       </c>
-      <c r="C17" s="126" t="s">
+      <c r="F17" s="132" t="s">
         <v>1414</v>
-      </c>
-      <c r="D17" s="126" t="s">
-        <v>1415</v>
-      </c>
-      <c r="E17" s="126" t="s">
-        <v>1416</v>
-      </c>
-      <c r="F17" s="132" t="s">
-        <v>1417</v>
       </c>
       <c r="G17" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H17" s="126" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="I17" s="126" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="J17" s="126"/>
       <c r="K17" s="126" t="s">
+        <v>1417</v>
+      </c>
+      <c r="L17" s="126" t="s">
+        <v>1418</v>
+      </c>
+      <c r="M17" s="126" t="s">
+        <v>1419</v>
+      </c>
+      <c r="N17" s="126" t="s">
         <v>1420</v>
       </c>
-      <c r="L17" s="126" t="s">
+      <c r="O17" s="126" t="s">
         <v>1421</v>
       </c>
-      <c r="M17" s="126" t="s">
-        <v>1422</v>
-      </c>
-      <c r="N17" s="126" t="s">
-        <v>1423</v>
-      </c>
-      <c r="O17" s="126" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A18" s="129" t="s">
         <v>596</v>
       </c>
       <c r="B18" s="126" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="C18" s="126"/>
       <c r="D18" s="126"/>
@@ -21962,10 +21953,10 @@
         <v>561</v>
       </c>
       <c r="H18" s="126" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="I18" s="126" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="J18" s="126"/>
       <c r="K18" s="126"/>
@@ -21974,114 +21965,114 @@
       <c r="N18" s="126"/>
       <c r="O18" s="126"/>
     </row>
-    <row r="19" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A19" s="129" t="s">
         <v>596</v>
       </c>
       <c r="B19" s="126" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C19" s="126" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D19" s="126" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E19" s="126" t="s">
         <v>1428</v>
       </c>
-      <c r="C19" s="126" t="s">
+      <c r="F19" s="126" t="s">
         <v>1429</v>
-      </c>
-      <c r="D19" s="126" t="s">
-        <v>1430</v>
-      </c>
-      <c r="E19" s="126" t="s">
-        <v>1431</v>
-      </c>
-      <c r="F19" s="126" t="s">
-        <v>1432</v>
       </c>
       <c r="G19" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H19" s="126" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="I19" s="126" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="J19" s="126"/>
       <c r="K19" s="126" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="L19" s="126" t="s">
         <v>404</v>
       </c>
       <c r="M19" s="126" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="N19" s="126" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="O19" s="126" t="s">
-        <v>1438</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="129" t="s">
         <v>577</v>
       </c>
       <c r="B20" s="126" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C20" s="126" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D20" s="126" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E20" s="126" t="s">
         <v>1439</v>
       </c>
-      <c r="C20" s="126" t="s">
+      <c r="F20" s="126" t="s">
         <v>1440</v>
-      </c>
-      <c r="D20" s="126" t="s">
-        <v>1441</v>
-      </c>
-      <c r="E20" s="126" t="s">
-        <v>1442</v>
-      </c>
-      <c r="F20" s="126" t="s">
-        <v>1443</v>
       </c>
       <c r="G20" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H20" s="126" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="I20" s="126"/>
       <c r="J20" s="126" t="s">
+        <v>1442</v>
+      </c>
+      <c r="K20" s="126" t="s">
+        <v>1443</v>
+      </c>
+      <c r="L20" s="126" t="s">
+        <v>1444</v>
+      </c>
+      <c r="M20" s="126" t="s">
         <v>1445</v>
       </c>
-      <c r="K20" s="126" t="s">
+      <c r="N20" s="126" t="s">
         <v>1446</v>
       </c>
-      <c r="L20" s="126" t="s">
+      <c r="O20" s="126" t="s">
         <v>1447</v>
       </c>
-      <c r="M20" s="126" t="s">
-        <v>1448</v>
-      </c>
-      <c r="N20" s="126" t="s">
-        <v>1449</v>
-      </c>
-      <c r="O20" s="126" t="s">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A21" s="129" t="s">
         <v>588</v>
       </c>
       <c r="B21" s="126" t="s">
+        <v>348</v>
+      </c>
+      <c r="C21" s="126" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D21" s="126" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E21" s="126" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F21" s="126" t="s">
         <v>1451</v>
-      </c>
-      <c r="C21" s="126" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D21" s="126" t="s">
-        <v>1453</v>
-      </c>
-      <c r="E21" s="126" t="s">
-        <v>1454</v>
-      </c>
-      <c r="F21" s="126" t="s">
-        <v>1455</v>
       </c>
       <c r="G21" s="126" t="s">
         <v>561</v>
@@ -22095,7 +22086,7 @@
       <c r="N21" s="126"/>
       <c r="O21" s="126"/>
     </row>
-    <row r="22" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>607</v>
       </c>
@@ -22103,41 +22094,41 @@
         <v>608</v>
       </c>
       <c r="C22" s="126" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="D22" s="126" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="E22" s="126" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="F22" s="126" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="G22" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H22" s="126" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="I22" s="126" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="J22" s="126"/>
       <c r="K22" s="126" t="s">
+        <v>1458</v>
+      </c>
+      <c r="L22" s="126" t="s">
+        <v>1459</v>
+      </c>
+      <c r="M22" s="126" t="s">
+        <v>1460</v>
+      </c>
+      <c r="N22" s="126" t="s">
+        <v>1461</v>
+      </c>
+      <c r="O22" s="126" t="s">
         <v>1462</v>
-      </c>
-      <c r="L22" s="126" t="s">
-        <v>1463</v>
-      </c>
-      <c r="M22" s="126" t="s">
-        <v>1464</v>
-      </c>
-      <c r="N22" s="126" t="s">
-        <v>1465</v>
-      </c>
-      <c r="O22" s="126" t="s">
-        <v>1466</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -22145,92 +22136,92 @@
         <v>568</v>
       </c>
       <c r="B23" s="126" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C23" s="126" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D23" s="126" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E23" s="126" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F23" s="126" t="s">
         <v>1467</v>
-      </c>
-      <c r="C23" s="126" t="s">
-        <v>1468</v>
-      </c>
-      <c r="D23" s="126" t="s">
-        <v>1469</v>
-      </c>
-      <c r="E23" s="126" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F23" s="126" t="s">
-        <v>1471</v>
       </c>
       <c r="G23" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H23" s="126" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="I23" s="126" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="J23" s="126"/>
       <c r="K23" s="126" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="L23" s="126" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="M23" s="126" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="N23" s="126" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="O23" s="126" t="s">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A24" s="129" t="s">
         <v>568</v>
       </c>
       <c r="B24" s="126" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C24" s="126" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D24" s="126" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E24" s="126" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F24" s="126" t="s">
         <v>1478</v>
-      </c>
-      <c r="C24" s="126" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D24" s="126" t="s">
-        <v>1480</v>
-      </c>
-      <c r="E24" s="126" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F24" s="126" t="s">
-        <v>1482</v>
       </c>
       <c r="G24" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H24" s="126" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="I24" s="126" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="J24" s="126"/>
       <c r="K24" s="126" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="L24" s="126" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="M24" s="126" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="N24" s="126" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="O24" s="126" t="s">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A25" s="129" t="s">
         <v>568</v>
       </c>
@@ -22238,42 +22229,42 @@
         <v>961</v>
       </c>
       <c r="C25" s="126" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="D25" s="126" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="E25" s="126" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="F25" s="126" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="G25" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H25" s="126" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="I25" s="126"/>
       <c r="J25" s="126"/>
       <c r="K25" s="126" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="L25" s="126" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="M25" s="126" t="s">
         <v>404</v>
       </c>
       <c r="N25" s="126" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="O25" s="126" t="s">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>568</v>
       </c>
@@ -22281,71 +22272,71 @@
         <v>581</v>
       </c>
       <c r="C26" s="126" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="D26" s="126" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="E26" s="126" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="F26" s="126" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="G26" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H26" s="126" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="I26" s="126"/>
       <c r="J26" s="126"/>
       <c r="K26" s="126" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="L26" s="126" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="M26" s="126" t="s">
         <v>404</v>
       </c>
       <c r="N26" s="126" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="O26" s="126" t="s">
-        <v>1506</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A27" s="129" t="s">
         <v>590</v>
       </c>
       <c r="B27" s="126" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C27" s="126" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D27" s="126" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E27" s="126" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F27" s="126" t="s">
         <v>1507</v>
-      </c>
-      <c r="C27" s="126" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D27" s="126" t="s">
-        <v>1509</v>
-      </c>
-      <c r="E27" s="126" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F27" s="126" t="s">
-        <v>1511</v>
       </c>
       <c r="G27" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H27" s="126" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="I27" s="126" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="J27" s="126" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="K27" s="126" t="s">
         <v>404</v>
@@ -22357,65 +22348,58 @@
         <v>404</v>
       </c>
       <c r="N27" s="126" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="O27" s="126" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A28" s="129" t="s">
         <v>590</v>
       </c>
       <c r="B28" s="126" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C28" s="126" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D28" s="126" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E28" s="126" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F28" s="126" t="s">
         <v>1516</v>
-      </c>
-      <c r="C28" s="126" t="s">
-        <v>1517</v>
-      </c>
-      <c r="D28" s="126" t="s">
-        <v>1518</v>
-      </c>
-      <c r="E28" s="126" t="s">
-        <v>1519</v>
-      </c>
-      <c r="F28" s="126" t="s">
-        <v>1520</v>
       </c>
       <c r="G28" s="126" t="s">
         <v>561</v>
       </c>
       <c r="H28" s="126" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="I28" s="126"/>
       <c r="J28" s="126" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="K28" s="126" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="L28" s="126" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="M28" s="126" t="s">
         <v>404</v>
       </c>
       <c r="N28" s="126" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="O28" s="126" t="s">
         <v>404</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q28" xr:uid="{980A29CF-D105-47BF-A299-22EED3F87C99}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="REGISTRO Y CONTROL"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <conditionalFormatting sqref="B7">
     <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
@@ -22437,6 +22421,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5292D3F-0B6E-46E3-A044-1C46EB00664B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -22460,7 +22445,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>542</v>
       </c>
@@ -22474,7 +22459,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="115" t="s">
         <v>545</v>
       </c>
@@ -22488,7 +22473,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>548</v>
       </c>
@@ -22502,7 +22487,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>550</v>
       </c>
@@ -22516,7 +22501,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>545</v>
       </c>
@@ -22530,7 +22515,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>542</v>
       </c>
@@ -22544,7 +22529,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>550</v>
       </c>
@@ -22558,7 +22543,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>559</v>
       </c>
@@ -22572,7 +22557,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>559</v>
       </c>
@@ -22586,7 +22571,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>559</v>
       </c>
@@ -22600,7 +22585,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>559</v>
       </c>
@@ -22614,7 +22599,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>559</v>
       </c>
@@ -22628,7 +22613,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="115" t="s">
         <v>548</v>
       </c>
@@ -22642,7 +22627,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>542</v>
       </c>
@@ -22656,7 +22641,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>550</v>
       </c>
@@ -22670,7 +22655,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>550</v>
       </c>
@@ -22684,7 +22669,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>550</v>
       </c>
@@ -22698,7 +22683,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="115" t="s">
         <v>548</v>
       </c>
@@ -22712,7 +22697,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="115" t="s">
         <v>548</v>
       </c>
@@ -22726,7 +22711,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>559</v>
       </c>
@@ -22740,7 +22725,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>550</v>
       </c>
@@ -22754,7 +22739,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>550</v>
       </c>
@@ -22768,7 +22753,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="115" t="s">
         <v>548</v>
       </c>
@@ -22782,7 +22767,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="115" t="s">
         <v>582</v>
       </c>
@@ -22796,7 +22781,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>559</v>
       </c>
@@ -22810,7 +22795,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>559</v>
       </c>
@@ -22824,7 +22809,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>548</v>
       </c>
@@ -22852,7 +22837,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>548</v>
       </c>
@@ -22866,7 +22851,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>550</v>
       </c>
@@ -22880,7 +22865,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>542</v>
       </c>
@@ -22894,7 +22879,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>548</v>
       </c>
@@ -22908,7 +22893,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>559</v>
       </c>
@@ -22922,7 +22907,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>559</v>
       </c>
@@ -22936,7 +22921,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>559</v>
       </c>
@@ -22950,7 +22935,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>542</v>
       </c>
@@ -22964,7 +22949,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="115" t="s">
         <v>548</v>
       </c>
@@ -22978,7 +22963,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>542</v>
       </c>
@@ -22992,7 +22977,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>559</v>
       </c>
@@ -23006,7 +22991,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>548</v>
       </c>
@@ -23048,7 +23033,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="115" t="s">
         <v>606</v>
       </c>
@@ -23062,7 +23047,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>559</v>
       </c>
@@ -23076,7 +23061,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="115" t="s">
         <v>545</v>
       </c>
@@ -23090,7 +23075,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>559</v>
       </c>
@@ -23104,7 +23089,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>559</v>
       </c>
@@ -23118,7 +23103,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="115" t="s">
         <v>606</v>
       </c>
@@ -23132,7 +23117,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="115" t="s">
         <v>606</v>
       </c>
@@ -23146,7 +23131,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="115" t="s">
         <v>545</v>
       </c>
@@ -23174,7 +23159,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="115" t="s">
         <v>582</v>
       </c>
@@ -23189,7 +23174,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D53" xr:uid="{D5292D3F-0B6E-46E3-A044-1C46EB00664B}"/>
+  <autoFilter ref="A1:D53" xr:uid="{D5292D3F-0B6E-46E3-A044-1C46EB00664B}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="DOCENCIA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="B3">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>

--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="386" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03C5AEF0-A5A8-4E17-8954-9522B0CC61BB}"/>
+  <xr:revisionPtr revIDLastSave="393" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{489019DA-7577-4848-8696-C48DF6AC8391}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Retos" sheetId="4" r:id="rId1"/>
@@ -7423,12 +7423,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7438,6 +7432,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8083,6 +8083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5CC9271-A20F-4DAE-A693-53F4455B4AEF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L289"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8131,7 +8132,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>627</v>
       </c>
@@ -8157,7 +8158,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>627</v>
       </c>
@@ -8183,7 +8184,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>627</v>
       </c>
@@ -8212,7 +8213,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>640</v>
       </c>
@@ -8235,7 +8236,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>640</v>
       </c>
@@ -8258,7 +8259,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>647</v>
       </c>
@@ -8287,7 +8288,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>652</v>
       </c>
@@ -8313,7 +8314,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>652</v>
       </c>
@@ -8342,7 +8343,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>652</v>
       </c>
@@ -8368,7 +8369,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>652</v>
       </c>
@@ -8397,7 +8398,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>652</v>
       </c>
@@ -8420,7 +8421,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>668</v>
       </c>
@@ -8443,7 +8444,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>671</v>
       </c>
@@ -8469,7 +8470,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>671</v>
       </c>
@@ -8495,7 +8496,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>678</v>
       </c>
@@ -8518,7 +8519,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>682</v>
       </c>
@@ -8556,7 +8557,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>682</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>682</v>
       </c>
@@ -8608,7 +8609,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>682</v>
       </c>
@@ -8637,7 +8638,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>690</v>
       </c>
@@ -8660,7 +8661,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>690</v>
       </c>
@@ -8683,7 +8684,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>695</v>
       </c>
@@ -8703,7 +8704,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>695</v>
       </c>
@@ -8729,7 +8730,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>700</v>
       </c>
@@ -8755,7 +8756,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>700</v>
       </c>
@@ -8781,7 +8782,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>700</v>
       </c>
@@ -8807,7 +8808,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>700</v>
       </c>
@@ -8833,7 +8834,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>700</v>
       </c>
@@ -8859,7 +8860,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>700</v>
       </c>
@@ -8882,7 +8883,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>716</v>
       </c>
@@ -8905,7 +8906,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>716</v>
       </c>
@@ -8926,7 +8927,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>721</v>
       </c>
@@ -8946,7 +8947,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>721</v>
       </c>
@@ -8966,7 +8967,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>721</v>
       </c>
@@ -8986,7 +8987,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>728</v>
       </c>
@@ -9015,7 +9016,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>728</v>
       </c>
@@ -9044,7 +9045,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>728</v>
       </c>
@@ -9073,7 +9074,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>728</v>
       </c>
@@ -9102,7 +9103,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>728</v>
       </c>
@@ -9131,7 +9132,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>743</v>
       </c>
@@ -9151,7 +9152,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>743</v>
       </c>
@@ -9171,7 +9172,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>748</v>
       </c>
@@ -9194,7 +9195,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>748</v>
       </c>
@@ -9217,7 +9218,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>748</v>
       </c>
@@ -9243,7 +9244,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>748</v>
       </c>
@@ -9272,7 +9273,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>760</v>
       </c>
@@ -9298,7 +9299,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>760</v>
       </c>
@@ -9324,7 +9325,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>766</v>
       </c>
@@ -9347,7 +9348,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>766</v>
       </c>
@@ -9370,7 +9371,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>766</v>
       </c>
@@ -9396,7 +9397,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>775</v>
       </c>
@@ -9425,7 +9426,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>775</v>
       </c>
@@ -9454,7 +9455,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>775</v>
       </c>
@@ -9483,7 +9484,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>775</v>
       </c>
@@ -9512,7 +9513,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>775</v>
       </c>
@@ -9541,7 +9542,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>778</v>
       </c>
@@ -9567,7 +9568,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>778</v>
       </c>
@@ -9593,7 +9594,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>778</v>
       </c>
@@ -9616,7 +9617,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>788</v>
       </c>
@@ -9642,7 +9643,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>788</v>
       </c>
@@ -9668,7 +9669,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>788</v>
       </c>
@@ -9706,7 +9707,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>788</v>
       </c>
@@ -9744,7 +9745,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>794</v>
       </c>
@@ -9764,7 +9765,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>794</v>
       </c>
@@ -9784,7 +9785,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>794</v>
       </c>
@@ -9914,33 +9915,33 @@
         <v>603</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="71" spans="1:12" s="123" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="123" t="s">
         <v>811</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="123" t="s">
         <v>812</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="123" t="s">
         <v>813</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="123" t="s">
         <v>630</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="123" t="s">
         <v>814</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G71" s="123" t="s">
         <v>632</v>
       </c>
-      <c r="K71" t="s">
-        <v>587</v>
-      </c>
-      <c r="L71" t="s">
+      <c r="K71" s="123" t="s">
+        <v>595</v>
+      </c>
+      <c r="L71" s="123" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>815</v>
       </c>
@@ -9966,7 +9967,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>819</v>
       </c>
@@ -9995,7 +9996,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>819</v>
       </c>
@@ -10021,7 +10022,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>819</v>
       </c>
@@ -10044,7 +10045,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>819</v>
       </c>
@@ -10070,7 +10071,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>819</v>
       </c>
@@ -10096,7 +10097,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>834</v>
       </c>
@@ -10122,7 +10123,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>834</v>
       </c>
@@ -10148,7 +10149,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>840</v>
       </c>
@@ -10174,7 +10175,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>840</v>
       </c>
@@ -10200,7 +10201,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>846</v>
       </c>
@@ -10229,7 +10230,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>846</v>
       </c>
@@ -10258,7 +10259,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>846</v>
       </c>
@@ -10287,7 +10288,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>846</v>
       </c>
@@ -10316,7 +10317,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>856</v>
       </c>
@@ -10342,7 +10343,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>856</v>
       </c>
@@ -10365,7 +10366,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>856</v>
       </c>
@@ -10388,7 +10389,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>866</v>
       </c>
@@ -10414,7 +10415,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>866</v>
       </c>
@@ -10440,7 +10441,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>866</v>
       </c>
@@ -10466,7 +10467,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>866</v>
       </c>
@@ -10489,7 +10490,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>866</v>
       </c>
@@ -10512,7 +10513,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>880</v>
       </c>
@@ -10538,7 +10539,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>880</v>
       </c>
@@ -10561,7 +10562,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>880</v>
       </c>
@@ -10584,7 +10585,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>888</v>
       </c>
@@ -10613,7 +10614,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>888</v>
       </c>
@@ -10642,7 +10643,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>888</v>
       </c>
@@ -10677,7 +10678,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>888</v>
       </c>
@@ -10706,7 +10707,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>888</v>
       </c>
@@ -10729,7 +10730,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>899</v>
       </c>
@@ -10752,7 +10753,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>899</v>
       </c>
@@ -10775,7 +10776,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>899</v>
       </c>
@@ -10801,7 +10802,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>905</v>
       </c>
@@ -10824,7 +10825,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>905</v>
       </c>
@@ -10850,7 +10851,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>905</v>
       </c>
@@ -10873,7 +10874,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>910</v>
       </c>
@@ -10899,7 +10900,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>913</v>
       </c>
@@ -10922,7 +10923,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>913</v>
       </c>
@@ -10951,7 +10952,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>913</v>
       </c>
@@ -10977,7 +10978,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>913</v>
       </c>
@@ -11000,7 +11001,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>913</v>
       </c>
@@ -11023,7 +11024,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>913</v>
       </c>
@@ -11046,7 +11047,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>913</v>
       </c>
@@ -11069,7 +11070,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>913</v>
       </c>
@@ -11092,7 +11093,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>936</v>
       </c>
@@ -11115,7 +11116,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>936</v>
       </c>
@@ -11138,7 +11139,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>936</v>
       </c>
@@ -11167,7 +11168,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>936</v>
       </c>
@@ -11196,7 +11197,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>948</v>
       </c>
@@ -11219,7 +11220,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>948</v>
       </c>
@@ -11242,7 +11243,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>948</v>
       </c>
@@ -11271,7 +11272,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>948</v>
       </c>
@@ -11300,7 +11301,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>955</v>
       </c>
@@ -11323,7 +11324,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>955</v>
       </c>
@@ -11346,7 +11347,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>955</v>
       </c>
@@ -11375,7 +11376,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>955</v>
       </c>
@@ -11398,7 +11399,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>964</v>
       </c>
@@ -11421,7 +11422,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>964</v>
       </c>
@@ -11444,7 +11445,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>964</v>
       </c>
@@ -11473,7 +11474,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>964</v>
       </c>
@@ -11502,7 +11503,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>971</v>
       </c>
@@ -11525,7 +11526,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>971</v>
       </c>
@@ -11548,7 +11549,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>971</v>
       </c>
@@ -11571,7 +11572,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>971</v>
       </c>
@@ -11600,7 +11601,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>971</v>
       </c>
@@ -11629,7 +11630,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>980</v>
       </c>
@@ -11652,7 +11653,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>980</v>
       </c>
@@ -11675,7 +11676,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>980</v>
       </c>
@@ -11698,7 +11699,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>980</v>
       </c>
@@ -11721,7 +11722,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>980</v>
       </c>
@@ -11750,7 +11751,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>980</v>
       </c>
@@ -11773,7 +11774,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>992</v>
       </c>
@@ -11796,7 +11797,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>992</v>
       </c>
@@ -11819,7 +11820,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>992</v>
       </c>
@@ -11848,7 +11849,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>992</v>
       </c>
@@ -11877,7 +11878,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>998</v>
       </c>
@@ -11900,7 +11901,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>998</v>
       </c>
@@ -11923,7 +11924,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>998</v>
       </c>
@@ -11949,7 +11950,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>998</v>
       </c>
@@ -11972,7 +11973,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>998</v>
       </c>
@@ -11998,7 +11999,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>998</v>
       </c>
@@ -12021,7 +12022,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>998</v>
       </c>
@@ -12044,7 +12045,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>1016</v>
       </c>
@@ -12067,7 +12068,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>1016</v>
       </c>
@@ -12090,7 +12091,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>1016</v>
       </c>
@@ -12119,7 +12120,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>1016</v>
       </c>
@@ -12148,7 +12149,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>1025</v>
       </c>
@@ -12171,7 +12172,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>1025</v>
       </c>
@@ -12194,7 +12195,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>1025</v>
       </c>
@@ -12223,7 +12224,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>1025</v>
       </c>
@@ -12252,7 +12253,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>1025</v>
       </c>
@@ -12275,7 +12276,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>1034</v>
       </c>
@@ -12298,7 +12299,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>1034</v>
       </c>
@@ -12321,7 +12322,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>1034</v>
       </c>
@@ -12350,7 +12351,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>1034</v>
       </c>
@@ -12379,7 +12380,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>1037</v>
       </c>
@@ -12402,7 +12403,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>1037</v>
       </c>
@@ -12425,7 +12426,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>1037</v>
       </c>
@@ -12454,7 +12455,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>1037</v>
       </c>
@@ -12483,7 +12484,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1044</v>
       </c>
@@ -12503,7 +12504,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>1044</v>
       </c>
@@ -12523,7 +12524,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>1044</v>
       </c>
@@ -12543,7 +12544,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>1050</v>
       </c>
@@ -12566,7 +12567,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>1050</v>
       </c>
@@ -12589,7 +12590,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>1050</v>
       </c>
@@ -12618,7 +12619,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>1050</v>
       </c>
@@ -12647,7 +12648,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>1056</v>
       </c>
@@ -12670,7 +12671,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>1056</v>
       </c>
@@ -12699,7 +12700,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>1056</v>
       </c>
@@ -12722,7 +12723,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>1056</v>
       </c>
@@ -12751,7 +12752,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>1060</v>
       </c>
@@ -12774,7 +12775,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>1060</v>
       </c>
@@ -12797,7 +12798,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>1060</v>
       </c>
@@ -12826,7 +12827,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>1060</v>
       </c>
@@ -12855,7 +12856,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>1066</v>
       </c>
@@ -12878,7 +12879,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>1066</v>
       </c>
@@ -12904,7 +12905,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>1066</v>
       </c>
@@ -12927,7 +12928,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>1066</v>
       </c>
@@ -12956,7 +12957,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>1071</v>
       </c>
@@ -12979,7 +12980,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>1071</v>
       </c>
@@ -13003,7 +13004,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1071</v>
       </c>
@@ -13023,7 +13024,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1071</v>
       </c>
@@ -13043,7 +13044,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1071</v>
       </c>
@@ -13063,7 +13064,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>1071</v>
       </c>
@@ -13086,7 +13087,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1071</v>
       </c>
@@ -13106,7 +13107,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1071</v>
       </c>
@@ -13129,7 +13130,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1071</v>
       </c>
@@ -13152,7 +13153,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>1071</v>
       </c>
@@ -13172,7 +13173,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1071</v>
       </c>
@@ -13195,7 +13196,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1071</v>
       </c>
@@ -13221,7 +13222,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1071</v>
       </c>
@@ -13241,7 +13242,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1071</v>
       </c>
@@ -13270,7 +13271,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1102</v>
       </c>
@@ -13290,7 +13291,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1102</v>
       </c>
@@ -13310,7 +13311,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1106</v>
       </c>
@@ -13330,7 +13331,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1106</v>
       </c>
@@ -13350,7 +13351,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>1106</v>
       </c>
@@ -13370,7 +13371,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>1106</v>
       </c>
@@ -13390,7 +13391,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>1106</v>
       </c>
@@ -13410,7 +13411,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>1106</v>
       </c>
@@ -13430,7 +13431,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>1106</v>
       </c>
@@ -13450,7 +13451,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>1106</v>
       </c>
@@ -13470,7 +13471,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>1106</v>
       </c>
@@ -13490,7 +13491,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>1123</v>
       </c>
@@ -13513,7 +13514,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>1123</v>
       </c>
@@ -13536,7 +13537,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>1123</v>
       </c>
@@ -13565,7 +13566,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>1123</v>
       </c>
@@ -13594,7 +13595,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>1131</v>
       </c>
@@ -13617,7 +13618,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>1131</v>
       </c>
@@ -13640,7 +13641,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>1131</v>
       </c>
@@ -13669,7 +13670,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>1131</v>
       </c>
@@ -13692,7 +13693,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>1131</v>
       </c>
@@ -13721,7 +13722,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>1138</v>
       </c>
@@ -13741,7 +13742,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1138</v>
       </c>
@@ -13761,7 +13762,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>1138</v>
       </c>
@@ -13781,7 +13782,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1138</v>
       </c>
@@ -13801,7 +13802,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>1142</v>
       </c>
@@ -13821,7 +13822,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>1144</v>
       </c>
@@ -13841,7 +13842,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1145</v>
       </c>
@@ -13861,7 +13862,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1145</v>
       </c>
@@ -13881,7 +13882,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1145</v>
       </c>
@@ -13901,7 +13902,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>1145</v>
       </c>
@@ -13921,7 +13922,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1149</v>
       </c>
@@ -13941,7 +13942,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1149</v>
       </c>
@@ -13961,7 +13962,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1149</v>
       </c>
@@ -13981,7 +13982,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1149</v>
       </c>
@@ -14001,7 +14002,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1152</v>
       </c>
@@ -14030,7 +14031,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1157</v>
       </c>
@@ -14059,7 +14060,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1157</v>
       </c>
@@ -14088,7 +14089,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1157</v>
       </c>
@@ -14117,7 +14118,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1157</v>
       </c>
@@ -14146,7 +14147,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1157</v>
       </c>
@@ -14178,7 +14179,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1157</v>
       </c>
@@ -14207,7 +14208,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1157</v>
       </c>
@@ -14291,29 +14292,29 @@
         <v>603</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
+    <row r="249" spans="1:12" s="123" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="123" t="s">
         <v>1168</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="123" t="s">
         <v>881</v>
       </c>
-      <c r="C249" t="s">
+      <c r="C249" s="123" t="s">
         <v>1172</v>
       </c>
-      <c r="D249" t="s">
+      <c r="D249" s="123" t="s">
         <v>630</v>
       </c>
-      <c r="E249" t="s">
+      <c r="E249" s="123" t="s">
         <v>883</v>
       </c>
-      <c r="G249" t="s">
+      <c r="G249" s="123" t="s">
         <v>632</v>
       </c>
-      <c r="K249" t="s">
+      <c r="K249" s="123" t="s">
         <v>587</v>
       </c>
-      <c r="L249" t="s">
+      <c r="L249" s="123" t="s">
         <v>603</v>
       </c>
     </row>
@@ -14392,7 +14393,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1175</v>
       </c>
@@ -14412,7 +14413,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1177</v>
       </c>
@@ -14432,7 +14433,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1177</v>
       </c>
@@ -14452,7 +14453,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1177</v>
       </c>
@@ -14472,7 +14473,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1184</v>
       </c>
@@ -14492,7 +14493,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1184</v>
       </c>
@@ -14512,7 +14513,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1188</v>
       </c>
@@ -14532,7 +14533,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1188</v>
       </c>
@@ -14552,7 +14553,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1192</v>
       </c>
@@ -14572,7 +14573,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1192</v>
       </c>
@@ -14592,7 +14593,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1193</v>
       </c>
@@ -14618,7 +14619,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1193</v>
       </c>
@@ -14644,7 +14645,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1193</v>
       </c>
@@ -14670,7 +14671,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1193</v>
       </c>
@@ -14696,7 +14697,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1193</v>
       </c>
@@ -14722,7 +14723,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1196</v>
       </c>
@@ -14748,7 +14749,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1200</v>
       </c>
@@ -14768,7 +14769,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1200</v>
       </c>
@@ -14788,7 +14789,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1204</v>
       </c>
@@ -14817,7 +14818,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1204</v>
       </c>
@@ -14846,7 +14847,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1204</v>
       </c>
@@ -14875,7 +14876,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1204</v>
       </c>
@@ -14904,7 +14905,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1204</v>
       </c>
@@ -14933,7 +14934,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1206</v>
       </c>
@@ -14953,7 +14954,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1207</v>
       </c>
@@ -14979,7 +14980,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1211</v>
       </c>
@@ -15002,7 +15003,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1215</v>
       </c>
@@ -15022,7 +15023,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1215</v>
       </c>
@@ -15042,7 +15043,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1215</v>
       </c>
@@ -15062,7 +15063,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1222</v>
       </c>
@@ -15085,7 +15086,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1222</v>
       </c>
@@ -15108,7 +15109,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1222</v>
       </c>
@@ -15134,7 +15135,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1230</v>
       </c>
@@ -15154,7 +15155,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1230</v>
       </c>
@@ -15174,7 +15175,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1230</v>
       </c>
@@ -15194,7 +15195,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1230</v>
       </c>
@@ -15214,7 +15215,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1230</v>
       </c>
@@ -15235,6 +15236,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L289" xr:uid="{D5CC9271-A20F-4DAE-A693-53F4455B4AEF}">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="Operaciones Académicas"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="K16">
     <cfRule type="duplicateValues" dxfId="27" priority="6"/>
   </conditionalFormatting>
@@ -16728,15 +16736,15 @@
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
       <c r="Q1"/>
-      <c r="R1" s="144" t="s">
+      <c r="R1" s="142" t="s">
         <v>174</v>
       </c>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="145"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
+      <c r="S1" s="143"/>
+      <c r="T1" s="143"/>
+      <c r="U1" s="143"/>
+      <c r="V1" s="143"/>
+      <c r="W1" s="143"/>
+      <c r="X1" s="143"/>
     </row>
     <row r="2" spans="1:24" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -17549,19 +17557,19 @@
       <c r="M15" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N15" s="140"/>
-      <c r="O15" s="140"/>
-      <c r="P15" s="142" t="s">
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="140" t="s">
         <v>263</v>
       </c>
-      <c r="Q15" s="142"/>
-      <c r="R15" s="142"/>
-      <c r="S15" s="142"/>
-      <c r="T15" s="142"/>
-      <c r="U15" s="142"/>
-      <c r="V15" s="142"/>
-      <c r="W15" s="142"/>
-      <c r="X15" s="142"/>
+      <c r="Q15" s="140"/>
+      <c r="R15" s="140"/>
+      <c r="S15" s="140"/>
+      <c r="T15" s="140"/>
+      <c r="U15" s="140"/>
+      <c r="V15" s="140"/>
+      <c r="W15" s="140"/>
+      <c r="X15" s="140"/>
     </row>
     <row r="16" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
@@ -17603,17 +17611,17 @@
       <c r="M16" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N16" s="141"/>
-      <c r="O16" s="141"/>
-      <c r="P16" s="143"/>
-      <c r="Q16" s="143"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="143"/>
-      <c r="T16" s="143"/>
-      <c r="U16" s="143"/>
-      <c r="V16" s="143"/>
-      <c r="W16" s="143"/>
-      <c r="X16" s="143"/>
+      <c r="N16" s="145"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="141"/>
+      <c r="Q16" s="141"/>
+      <c r="R16" s="141"/>
+      <c r="S16" s="141"/>
+      <c r="T16" s="141"/>
+      <c r="U16" s="141"/>
+      <c r="V16" s="141"/>
+      <c r="W16" s="141"/>
+      <c r="X16" s="141"/>
     </row>
     <row r="17" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
@@ -21156,6 +21164,11 @@
   </sheetData>
   <autoFilter ref="A2:X2" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}"/>
   <mergeCells count="12">
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
     <mergeCell ref="V15:V16"/>
     <mergeCell ref="W15:W16"/>
     <mergeCell ref="X15:X16"/>
@@ -21163,11 +21176,6 @@
     <mergeCell ref="S15:S16"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="U15:U16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="393" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{489019DA-7577-4848-8696-C48DF6AC8391}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A389E3C-6879-4910-9991-A8B9B9BB8796}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
+    <workbookView minimized="1" xWindow="6108" yWindow="3708" windowWidth="17280" windowHeight="8880" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Retos" sheetId="4" r:id="rId1"/>
@@ -7423,6 +7423,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7432,12 +7438,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9805,7 +9805,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>801</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>801</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>801</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>801</v>
       </c>
@@ -14237,7 +14237,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1168</v>
       </c>
@@ -14266,7 +14266,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1168</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="249" spans="1:12" s="123" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" s="123" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="123" t="s">
         <v>1168</v>
       </c>
@@ -14318,7 +14318,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1168</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1168</v>
       </c>
@@ -14367,7 +14367,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1168</v>
       </c>
@@ -15237,9 +15237,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L289" xr:uid="{D5CC9271-A20F-4DAE-A693-53F4455B4AEF}">
-    <filterColumn colId="11">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Operaciones Académicas"/>
+        <filter val="DIRECCIÓN DE OPERACIONES NUEVOS  NEGOCIOS"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -16736,15 +16736,15 @@
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
       <c r="Q1"/>
-      <c r="R1" s="142" t="s">
+      <c r="R1" s="144" t="s">
         <v>174</v>
       </c>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
     </row>
     <row r="2" spans="1:24" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -17557,19 +17557,19 @@
       <c r="M15" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N15" s="144"/>
-      <c r="O15" s="144"/>
-      <c r="P15" s="140" t="s">
+      <c r="N15" s="140"/>
+      <c r="O15" s="140"/>
+      <c r="P15" s="142" t="s">
         <v>263</v>
       </c>
-      <c r="Q15" s="140"/>
-      <c r="R15" s="140"/>
-      <c r="S15" s="140"/>
-      <c r="T15" s="140"/>
-      <c r="U15" s="140"/>
-      <c r="V15" s="140"/>
-      <c r="W15" s="140"/>
-      <c r="X15" s="140"/>
+      <c r="Q15" s="142"/>
+      <c r="R15" s="142"/>
+      <c r="S15" s="142"/>
+      <c r="T15" s="142"/>
+      <c r="U15" s="142"/>
+      <c r="V15" s="142"/>
+      <c r="W15" s="142"/>
+      <c r="X15" s="142"/>
     </row>
     <row r="16" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
@@ -17611,17 +17611,17 @@
       <c r="M16" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N16" s="145"/>
-      <c r="O16" s="145"/>
-      <c r="P16" s="141"/>
-      <c r="Q16" s="141"/>
-      <c r="R16" s="141"/>
-      <c r="S16" s="141"/>
-      <c r="T16" s="141"/>
-      <c r="U16" s="141"/>
-      <c r="V16" s="141"/>
-      <c r="W16" s="141"/>
-      <c r="X16" s="141"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="141"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="143"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="143"/>
+      <c r="T16" s="143"/>
+      <c r="U16" s="143"/>
+      <c r="V16" s="143"/>
+      <c r="W16" s="143"/>
+      <c r="X16" s="143"/>
     </row>
     <row r="17" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
@@ -21164,11 +21164,6 @@
   </sheetData>
   <autoFilter ref="A2:X2" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}"/>
   <mergeCells count="12">
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
     <mergeCell ref="V15:V16"/>
     <mergeCell ref="W15:W16"/>
     <mergeCell ref="X15:X16"/>
@@ -21176,6 +21171,11 @@
     <mergeCell ref="S15:S16"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="U15:U16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22470,7 +22470,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5292D3F-0B6E-46E3-A044-1C46EB00664B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -22494,7 +22493,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>541</v>
       </c>
@@ -22508,7 +22507,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="115" t="s">
         <v>544</v>
       </c>
@@ -22522,7 +22521,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>547</v>
       </c>
@@ -22536,7 +22535,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>549</v>
       </c>
@@ -22550,7 +22549,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>544</v>
       </c>
@@ -22564,7 +22563,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>541</v>
       </c>
@@ -22578,7 +22577,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>549</v>
       </c>
@@ -22592,7 +22591,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>558</v>
       </c>
@@ -22606,7 +22605,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>558</v>
       </c>
@@ -22620,7 +22619,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>558</v>
       </c>
@@ -22634,7 +22633,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>558</v>
       </c>
@@ -22648,7 +22647,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>558</v>
       </c>
@@ -22662,7 +22661,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="115" t="s">
         <v>547</v>
       </c>
@@ -22676,7 +22675,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>541</v>
       </c>
@@ -22690,7 +22689,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>549</v>
       </c>
@@ -22704,7 +22703,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>549</v>
       </c>
@@ -22718,7 +22717,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>549</v>
       </c>
@@ -22732,7 +22731,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="115" t="s">
         <v>547</v>
       </c>
@@ -22746,7 +22745,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="115" t="s">
         <v>547</v>
       </c>
@@ -22760,7 +22759,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>558</v>
       </c>
@@ -22774,7 +22773,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>549</v>
       </c>
@@ -22788,7 +22787,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>549</v>
       </c>
@@ -22802,7 +22801,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="115" t="s">
         <v>547</v>
       </c>
@@ -22816,7 +22815,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="115" t="s">
         <v>581</v>
       </c>
@@ -22830,7 +22829,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>558</v>
       </c>
@@ -22844,7 +22843,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>558</v>
       </c>
@@ -22858,7 +22857,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>547</v>
       </c>
@@ -22886,7 +22885,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>547</v>
       </c>
@@ -22900,7 +22899,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>549</v>
       </c>
@@ -22914,7 +22913,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>541</v>
       </c>
@@ -22928,7 +22927,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>547</v>
       </c>
@@ -22942,7 +22941,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>558</v>
       </c>
@@ -22956,7 +22955,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>558</v>
       </c>
@@ -22970,7 +22969,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>558</v>
       </c>
@@ -22984,7 +22983,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>541</v>
       </c>
@@ -22998,7 +22997,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="115" t="s">
         <v>547</v>
       </c>
@@ -23012,7 +23011,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>541</v>
       </c>
@@ -23026,7 +23025,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>558</v>
       </c>
@@ -23040,7 +23039,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>547</v>
       </c>
@@ -23082,7 +23081,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="115" t="s">
         <v>605</v>
       </c>
@@ -23096,7 +23095,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>558</v>
       </c>
@@ -23110,7 +23109,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="115" t="s">
         <v>544</v>
       </c>
@@ -23124,7 +23123,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>558</v>
       </c>
@@ -23138,7 +23137,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>558</v>
       </c>
@@ -23152,7 +23151,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="115" t="s">
         <v>605</v>
       </c>
@@ -23166,7 +23165,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="115" t="s">
         <v>605</v>
       </c>
@@ -23180,7 +23179,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="115" t="s">
         <v>544</v>
       </c>
@@ -23208,7 +23207,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="115" t="s">
         <v>581</v>
       </c>
@@ -23223,13 +23222,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D53" xr:uid="{D5292D3F-0B6E-46E3-A044-1C46EB00664B}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="DOCENCIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D53" xr:uid="{D5292D3F-0B6E-46E3-A044-1C46EB00664B}"/>
   <conditionalFormatting sqref="B3">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>

--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="398" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A389E3C-6879-4910-9991-A8B9B9BB8796}"/>
+  <xr:revisionPtr revIDLastSave="409" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E0482A5-0E60-46F7-8C37-EAEDAE8BDDA5}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6108" yWindow="3708" windowWidth="17280" windowHeight="8880" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Retos" sheetId="4" r:id="rId1"/>
@@ -6811,7 +6811,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6920,6 +6920,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -7021,7 +7027,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7423,12 +7429,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7440,6 +7440,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -8091,7 +8098,7 @@
     <col min="2" max="2" width="28.109375" customWidth="1"/>
     <col min="3" max="3" width="24.5546875" customWidth="1"/>
     <col min="4" max="4" width="17.5546875" customWidth="1"/>
-    <col min="5" max="5" width="17.88671875" customWidth="1"/>
+    <col min="5" max="5" width="45.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -9172,7 +9179,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>748</v>
       </c>
@@ -9195,7 +9202,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>748</v>
       </c>
@@ -9218,7 +9225,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>748</v>
       </c>
@@ -9231,7 +9238,7 @@
       <c r="D45" t="s">
         <v>630</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="146" t="s">
         <v>755</v>
       </c>
       <c r="G45" t="s">
@@ -9244,7 +9251,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>748</v>
       </c>
@@ -9915,7 +9922,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="71" spans="1:12" s="123" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" s="123" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="123" t="s">
         <v>811</v>
       </c>
@@ -15239,7 +15246,7 @@
   <autoFilter ref="A1:L289" xr:uid="{D5CC9271-A20F-4DAE-A693-53F4455B4AEF}">
     <filterColumn colId="0">
       <filters>
-        <filter val="DIRECCIÓN DE OPERACIONES NUEVOS  NEGOCIOS"/>
+        <filter val="DIRECCIÓN DE EXPERIENCIA E INCLUSIÓN"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -15285,7 +15292,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E8EE7F9-C83B-46E0-BD66-45A599C1C12A}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15324,7 +15330,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -15353,7 +15359,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -15382,7 +15388,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -15411,7 +15417,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -15440,7 +15446,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -15469,7 +15475,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -15498,7 +15504,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -15527,7 +15533,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
@@ -15556,7 +15562,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -15585,7 +15591,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -15614,7 +15620,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
@@ -15643,7 +15649,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -15672,7 +15678,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
@@ -15701,7 +15707,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>59</v>
       </c>
@@ -15730,7 +15736,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>63</v>
       </c>
@@ -15759,7 +15765,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>63</v>
       </c>
@@ -15788,7 +15794,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>70</v>
       </c>
@@ -15817,7 +15823,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
@@ -15846,7 +15852,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>70</v>
       </c>
@@ -15875,7 +15881,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>70</v>
       </c>
@@ -15904,7 +15910,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>84</v>
       </c>
@@ -15933,7 +15939,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -15962,7 +15968,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>91</v>
       </c>
@@ -15991,7 +15997,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>95</v>
       </c>
@@ -16020,7 +16026,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>99</v>
       </c>
@@ -16049,7 +16055,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>99</v>
       </c>
@@ -16078,7 +16084,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>107</v>
       </c>
@@ -16107,7 +16113,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>107</v>
       </c>
@@ -16136,7 +16142,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>115</v>
       </c>
@@ -16165,7 +16171,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>119</v>
       </c>
@@ -16190,7 +16196,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>122</v>
       </c>
@@ -16219,7 +16225,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>126</v>
       </c>
@@ -16246,7 +16252,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>126</v>
       </c>
@@ -16271,7 +16277,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>130</v>
       </c>
@@ -16300,7 +16306,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="82.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>130</v>
       </c>
@@ -16329,7 +16335,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>138</v>
       </c>
@@ -16358,7 +16364,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>138</v>
       </c>
@@ -16385,7 +16391,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>144</v>
       </c>
@@ -16414,7 +16420,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>144</v>
       </c>
@@ -16443,7 +16449,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>144</v>
       </c>
@@ -16472,7 +16478,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>156</v>
       </c>
@@ -16530,7 +16536,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>46</v>
       </c>
@@ -16559,7 +16565,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>119</v>
       </c>
@@ -16584,7 +16590,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="110.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>122</v>
       </c>
@@ -16611,7 +16617,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>144</v>
       </c>
@@ -16636,7 +16642,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>156</v>
       </c>
@@ -16662,13 +16668,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I48" xr:uid="{2E8EE7F9-C83B-46E0-BD66-45A599C1C12A}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="SOPHIA- Programación academica"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I48" xr:uid="{2E8EE7F9-C83B-46E0-BD66-45A599C1C12A}"/>
   <conditionalFormatting sqref="H3">
     <cfRule type="duplicateValues" dxfId="15" priority="12"/>
   </conditionalFormatting>
@@ -16736,15 +16736,15 @@
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
       <c r="Q1"/>
-      <c r="R1" s="144" t="s">
+      <c r="R1" s="142" t="s">
         <v>174</v>
       </c>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="145"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
+      <c r="S1" s="143"/>
+      <c r="T1" s="143"/>
+      <c r="U1" s="143"/>
+      <c r="V1" s="143"/>
+      <c r="W1" s="143"/>
+      <c r="X1" s="143"/>
     </row>
     <row r="2" spans="1:24" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -17557,19 +17557,19 @@
       <c r="M15" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N15" s="140"/>
-      <c r="O15" s="140"/>
-      <c r="P15" s="142" t="s">
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="140" t="s">
         <v>263</v>
       </c>
-      <c r="Q15" s="142"/>
-      <c r="R15" s="142"/>
-      <c r="S15" s="142"/>
-      <c r="T15" s="142"/>
-      <c r="U15" s="142"/>
-      <c r="V15" s="142"/>
-      <c r="W15" s="142"/>
-      <c r="X15" s="142"/>
+      <c r="Q15" s="140"/>
+      <c r="R15" s="140"/>
+      <c r="S15" s="140"/>
+      <c r="T15" s="140"/>
+      <c r="U15" s="140"/>
+      <c r="V15" s="140"/>
+      <c r="W15" s="140"/>
+      <c r="X15" s="140"/>
     </row>
     <row r="16" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
@@ -17611,17 +17611,17 @@
       <c r="M16" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N16" s="141"/>
-      <c r="O16" s="141"/>
-      <c r="P16" s="143"/>
-      <c r="Q16" s="143"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="143"/>
-      <c r="T16" s="143"/>
-      <c r="U16" s="143"/>
-      <c r="V16" s="143"/>
-      <c r="W16" s="143"/>
-      <c r="X16" s="143"/>
+      <c r="N16" s="145"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="141"/>
+      <c r="Q16" s="141"/>
+      <c r="R16" s="141"/>
+      <c r="S16" s="141"/>
+      <c r="T16" s="141"/>
+      <c r="U16" s="141"/>
+      <c r="V16" s="141"/>
+      <c r="W16" s="141"/>
+      <c r="X16" s="141"/>
     </row>
     <row r="17" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
@@ -21164,6 +21164,11 @@
   </sheetData>
   <autoFilter ref="A2:X2" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}"/>
   <mergeCells count="12">
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
     <mergeCell ref="V15:V16"/>
     <mergeCell ref="W15:W16"/>
     <mergeCell ref="X15:X16"/>
@@ -21171,11 +21176,6 @@
     <mergeCell ref="S15:S16"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="U15:U16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="409" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E0482A5-0E60-46F7-8C37-EAEDAE8BDDA5}"/>
+  <xr:revisionPtr revIDLastSave="414" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832D52BF-AD4E-428B-84D9-299B24A09C37}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Retos" sheetId="4" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Calidad!$A$1:$Q$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan de mejoramiento'!$A$2:$X$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan de mejoramiento'!$A$2:$X$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Proceso!$A$1:$D$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Proyectos!$A$1:$I$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Retos!$A$1:$L$289</definedName>
@@ -16702,6 +16702,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16820,7 +16821,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="202.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="202.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>189</v>
       </c>
@@ -16890,7 +16891,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="171.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>189</v>
       </c>
@@ -16958,7 +16959,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>189</v>
       </c>
@@ -17016,7 +17017,7 @@
       <c r="W5" s="25"/>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" spans="1:24" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="69" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>189</v>
       </c>
@@ -17074,7 +17075,7 @@
       <c r="W6" s="25"/>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" spans="1:24" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>220</v>
       </c>
@@ -17134,7 +17135,7 @@
       <c r="W7" s="36"/>
       <c r="X7" s="36"/>
     </row>
-    <row r="8" spans="1:24" ht="202.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="202.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="29" t="s">
         <v>220</v>
       </c>
@@ -17186,7 +17187,7 @@
       <c r="W8" s="36"/>
       <c r="X8" s="36"/>
     </row>
-    <row r="9" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="29" t="s">
         <v>220</v>
       </c>
@@ -17232,7 +17233,7 @@
       <c r="W9" s="36"/>
       <c r="X9" s="36"/>
     </row>
-    <row r="10" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="29" t="s">
         <v>220</v>
       </c>
@@ -17297,7 +17298,7 @@
       <c r="W10" s="36"/>
       <c r="X10" s="36"/>
     </row>
-    <row r="11" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="29" t="s">
         <v>220</v>
       </c>
@@ -17359,7 +17360,7 @@
       <c r="W11" s="36"/>
       <c r="X11" s="36"/>
     </row>
-    <row r="12" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="29" t="s">
         <v>220</v>
       </c>
@@ -17417,7 +17418,7 @@
       <c r="W12" s="36"/>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="1:24" ht="50.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" ht="50.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
         <v>248</v>
       </c>
@@ -17467,7 +17468,7 @@
       <c r="W13" s="25"/>
       <c r="X13" s="25"/>
     </row>
-    <row r="14" spans="1:24" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" ht="49.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
         <v>248</v>
       </c>
@@ -17517,7 +17518,7 @@
       <c r="W14" s="25"/>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="28" t="s">
         <v>248</v>
       </c>
@@ -17571,7 +17572,7 @@
       <c r="W15" s="140"/>
       <c r="X15" s="140"/>
     </row>
-    <row r="16" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
         <v>248</v>
       </c>
@@ -17623,7 +17624,7 @@
       <c r="W16" s="141"/>
       <c r="X16" s="141"/>
     </row>
-    <row r="17" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
         <v>248</v>
       </c>
@@ -17677,7 +17678,7 @@
       <c r="W17" s="19"/>
       <c r="X17" s="19"/>
     </row>
-    <row r="18" spans="1:24" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>248</v>
       </c>
@@ -17727,7 +17728,7 @@
       <c r="W18" s="25"/>
       <c r="X18" s="25"/>
     </row>
-    <row r="19" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
         <v>248</v>
       </c>
@@ -17777,7 +17778,7 @@
       <c r="W19" s="19"/>
       <c r="X19" s="19"/>
     </row>
-    <row r="20" spans="1:24" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" ht="31.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="28" t="s">
         <v>248</v>
       </c>
@@ -17825,7 +17826,7 @@
       <c r="W20" s="25"/>
       <c r="X20" s="25"/>
     </row>
-    <row r="21" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="28" t="s">
         <v>248</v>
       </c>
@@ -17873,7 +17874,7 @@
       <c r="W21" s="25"/>
       <c r="X21" s="25"/>
     </row>
-    <row r="22" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="28" t="s">
         <v>248</v>
       </c>
@@ -17923,7 +17924,7 @@
       <c r="W22" s="19"/>
       <c r="X22" s="19"/>
     </row>
-    <row r="23" spans="1:24" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="28" t="s">
         <v>248</v>
       </c>
@@ -17977,7 +17978,7 @@
       <c r="W23" s="25"/>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" spans="1:24" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="61" t="s">
         <v>289</v>
       </c>
@@ -18029,7 +18030,7 @@
       <c r="W24" s="19"/>
       <c r="X24" s="19"/>
     </row>
-    <row r="25" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="61" t="s">
         <v>289</v>
       </c>
@@ -18085,7 +18086,7 @@
       <c r="W25" s="19"/>
       <c r="X25" s="19"/>
     </row>
-    <row r="26" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="61" t="s">
         <v>289</v>
       </c>
@@ -18139,7 +18140,7 @@
       <c r="W26" s="19"/>
       <c r="X26" s="19"/>
     </row>
-    <row r="27" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="61" t="s">
         <v>289</v>
       </c>
@@ -18199,7 +18200,7 @@
       <c r="W27" s="19"/>
       <c r="X27" s="19"/>
     </row>
-    <row r="28" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="61" t="s">
         <v>289</v>
       </c>
@@ -18259,7 +18260,7 @@
       <c r="W28" s="19"/>
       <c r="X28" s="19"/>
     </row>
-    <row r="29" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="61" t="s">
         <v>289</v>
       </c>
@@ -18317,7 +18318,7 @@
       <c r="W29" s="19"/>
       <c r="X29" s="19"/>
     </row>
-    <row r="30" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="61" t="s">
         <v>289</v>
       </c>
@@ -18373,7 +18374,7 @@
       <c r="W30" s="19"/>
       <c r="X30" s="19"/>
     </row>
-    <row r="31" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="61" t="s">
         <v>289</v>
       </c>
@@ -18433,7 +18434,7 @@
       <c r="W31" s="19"/>
       <c r="X31" s="19"/>
     </row>
-    <row r="32" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="61" t="s">
         <v>289</v>
       </c>
@@ -18491,7 +18492,7 @@
       <c r="W32" s="19"/>
       <c r="X32" s="19"/>
     </row>
-    <row r="33" spans="1:24" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" ht="31.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="61" t="s">
         <v>289</v>
       </c>
@@ -18535,7 +18536,7 @@
       <c r="W33" s="25"/>
       <c r="X33" s="25"/>
     </row>
-    <row r="34" spans="1:24" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="49" t="s">
         <v>341</v>
       </c>
@@ -18587,7 +18588,7 @@
       <c r="W34" s="25"/>
       <c r="X34" s="25"/>
     </row>
-    <row r="35" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="49" t="s">
         <v>341</v>
       </c>
@@ -18635,7 +18636,7 @@
       <c r="W35" s="25"/>
       <c r="X35" s="25"/>
     </row>
-    <row r="36" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="61" t="s">
         <v>341</v>
       </c>
@@ -18693,7 +18694,7 @@
       <c r="W36" s="19"/>
       <c r="X36" s="19"/>
     </row>
-    <row r="37" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="49" t="s">
         <v>341</v>
       </c>
@@ -18741,7 +18742,7 @@
       <c r="W37" s="25"/>
       <c r="X37" s="25"/>
     </row>
-    <row r="38" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="61" t="s">
         <v>341</v>
       </c>
@@ -18793,7 +18794,7 @@
       <c r="W38" s="19"/>
       <c r="X38" s="19"/>
     </row>
-    <row r="39" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="61" t="s">
         <v>341</v>
       </c>
@@ -18841,7 +18842,7 @@
       <c r="W39" s="19"/>
       <c r="X39" s="19"/>
     </row>
-    <row r="40" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="61" t="s">
         <v>341</v>
       </c>
@@ -18891,7 +18892,7 @@
       <c r="W40" s="78"/>
       <c r="X40" s="78"/>
     </row>
-    <row r="41" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="30" t="s">
         <v>369</v>
       </c>
@@ -18951,7 +18952,7 @@
       <c r="W41" s="36"/>
       <c r="X41" s="36"/>
     </row>
-    <row r="42" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="30" t="s">
         <v>369</v>
       </c>
@@ -19005,7 +19006,7 @@
       <c r="W42" s="36"/>
       <c r="X42" s="36"/>
     </row>
-    <row r="43" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="30" t="s">
         <v>369</v>
       </c>
@@ -19059,7 +19060,7 @@
       <c r="W43" s="36"/>
       <c r="X43" s="36"/>
     </row>
-    <row r="44" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="30" t="s">
         <v>369</v>
       </c>
@@ -19107,7 +19108,7 @@
       <c r="W44" s="36"/>
       <c r="X44" s="36"/>
     </row>
-    <row r="45" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="30" t="s">
         <v>369</v>
       </c>
@@ -19163,7 +19164,7 @@
       <c r="W45" s="36"/>
       <c r="X45" s="36"/>
     </row>
-    <row r="46" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="30" t="s">
         <v>369</v>
       </c>
@@ -19215,7 +19216,7 @@
       <c r="W46" s="36"/>
       <c r="X46" s="36"/>
     </row>
-    <row r="47" spans="1:24" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" ht="31.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="72" t="s">
         <v>387</v>
       </c>
@@ -19313,7 +19314,7 @@
       <c r="W48" s="19"/>
       <c r="X48" s="19"/>
     </row>
-    <row r="49" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="64" t="s">
         <v>387</v>
       </c>
@@ -19409,7 +19410,7 @@
       <c r="W50" s="19"/>
       <c r="X50" s="19"/>
     </row>
-    <row r="51" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="64" t="s">
         <v>387</v>
       </c>
@@ -19461,7 +19462,7 @@
       <c r="W51" s="19"/>
       <c r="X51" s="19"/>
     </row>
-    <row r="52" spans="1:24" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72" t="s">
         <v>408</v>
       </c>
@@ -19515,7 +19516,7 @@
       <c r="W52" s="25"/>
       <c r="X52" s="25"/>
     </row>
-    <row r="53" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72" t="s">
         <v>408</v>
       </c>
@@ -19565,7 +19566,7 @@
       <c r="W53" s="19"/>
       <c r="X53" s="19"/>
     </row>
-    <row r="54" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72" t="s">
         <v>408</v>
       </c>
@@ -19621,7 +19622,7 @@
       <c r="W54" s="19"/>
       <c r="X54" s="19"/>
     </row>
-    <row r="55" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="72" t="s">
         <v>408</v>
       </c>
@@ -19679,7 +19680,7 @@
       <c r="W55" s="19"/>
       <c r="X55" s="19"/>
     </row>
-    <row r="56" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="72" t="s">
         <v>408</v>
       </c>
@@ -19737,7 +19738,7 @@
       <c r="W56" s="19"/>
       <c r="X56" s="19"/>
     </row>
-    <row r="57" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="72" t="s">
         <v>408</v>
       </c>
@@ -19795,7 +19796,7 @@
       <c r="W57" s="19"/>
       <c r="X57" s="19"/>
     </row>
-    <row r="58" spans="1:24" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="72" t="s">
         <v>433</v>
       </c>
@@ -19849,7 +19850,7 @@
       <c r="W58" s="25"/>
       <c r="X58" s="25"/>
     </row>
-    <row r="59" spans="1:24" ht="76.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" ht="76.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="64" t="s">
         <v>433</v>
       </c>
@@ -19899,7 +19900,7 @@
       <c r="W59" s="19"/>
       <c r="X59" s="19"/>
     </row>
-    <row r="60" spans="1:24" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" ht="67.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="72" t="s">
         <v>433</v>
       </c>
@@ -19945,7 +19946,7 @@
       <c r="W60" s="25"/>
       <c r="X60" s="25"/>
     </row>
-    <row r="61" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="64" t="s">
         <v>433</v>
       </c>
@@ -19995,7 +19996,7 @@
       <c r="W61" s="19"/>
       <c r="X61" s="19"/>
     </row>
-    <row r="62" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="64" t="s">
         <v>448</v>
       </c>
@@ -20049,7 +20050,7 @@
       <c r="W62" s="19"/>
       <c r="X62" s="19"/>
     </row>
-    <row r="63" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="64" t="s">
         <v>448</v>
       </c>
@@ -20103,7 +20104,7 @@
       <c r="W63" s="19"/>
       <c r="X63" s="19"/>
     </row>
-    <row r="64" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="72" t="s">
         <v>448</v>
       </c>
@@ -20149,7 +20150,7 @@
       <c r="W64" s="25"/>
       <c r="X64" s="25"/>
     </row>
-    <row r="65" spans="1:24" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:24" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="72" t="s">
         <v>448</v>
       </c>
@@ -20205,7 +20206,7 @@
       <c r="W65" s="25"/>
       <c r="X65" s="25"/>
     </row>
-    <row r="66" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="64" t="s">
         <v>448</v>
       </c>
@@ -20265,7 +20266,7 @@
       <c r="W66" s="19"/>
       <c r="X66" s="19"/>
     </row>
-    <row r="67" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="64" t="s">
         <v>448</v>
       </c>
@@ -20335,7 +20336,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="68" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="64" t="s">
         <v>448</v>
       </c>
@@ -20399,7 +20400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="64" t="s">
         <v>448</v>
       </c>
@@ -20453,7 +20454,7 @@
       <c r="W69" s="19"/>
       <c r="X69" s="19"/>
     </row>
-    <row r="70" spans="1:24" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:24" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="64" t="s">
         <v>448</v>
       </c>
@@ -20507,7 +20508,7 @@
       <c r="W70" s="19"/>
       <c r="X70" s="19"/>
     </row>
-    <row r="71" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="64" t="s">
         <v>486</v>
       </c>
@@ -20557,7 +20558,7 @@
       <c r="W71" s="19"/>
       <c r="X71" s="19"/>
     </row>
-    <row r="72" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="64" t="s">
         <v>486</v>
       </c>
@@ -20605,7 +20606,7 @@
       <c r="W72" s="19"/>
       <c r="X72" s="19"/>
     </row>
-    <row r="73" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="64" t="s">
         <v>486</v>
       </c>
@@ -20657,7 +20658,7 @@
       <c r="W73" s="19"/>
       <c r="X73" s="19"/>
     </row>
-    <row r="74" spans="1:24" ht="156" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:24" ht="156" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="64" t="s">
         <v>486</v>
       </c>
@@ -20715,7 +20716,7 @@
       <c r="W74" s="19"/>
       <c r="X74" s="19"/>
     </row>
-    <row r="75" spans="1:24" ht="156" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:24" ht="156" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="64" t="s">
         <v>486</v>
       </c>
@@ -20773,7 +20774,7 @@
       <c r="W75" s="19"/>
       <c r="X75" s="19"/>
     </row>
-    <row r="76" spans="1:24" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:24" ht="124.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="72" t="s">
         <v>486</v>
       </c>
@@ -20829,7 +20830,7 @@
       <c r="W76" s="25"/>
       <c r="X76" s="25"/>
     </row>
-    <row r="77" spans="1:24" ht="156" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:24" ht="156" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="64" t="s">
         <v>486</v>
       </c>
@@ -20883,7 +20884,7 @@
       <c r="W77" s="19"/>
       <c r="X77" s="19"/>
     </row>
-    <row r="78" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="64" t="s">
         <v>486</v>
       </c>
@@ -21051,7 +21052,7 @@
       <c r="W80" s="25"/>
       <c r="X80" s="25"/>
     </row>
-    <row r="81" spans="1:24" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A81" s="72" t="s">
         <v>516</v>
       </c>
@@ -21162,7 +21163,13 @@
       <c r="X82" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:X2" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}"/>
+  <autoFilter ref="A2:X82" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="EXTENSIÓN"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="12">
     <mergeCell ref="N15:N16"/>
     <mergeCell ref="O15:O16"/>
@@ -22449,6 +22456,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q28" xr:uid="{980A29CF-D105-47BF-A299-22EED3F87C99}"/>
   <conditionalFormatting sqref="B7">
     <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>

--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="414" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832D52BF-AD4E-428B-84D9-299B24A09C37}"/>
+  <xr:revisionPtr revIDLastSave="454" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82ED1B49-2BC9-450F-B912-6E19EFD6CA2D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4223" uniqueCount="1525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="1528">
   <si>
     <t>Nombre del Proyecto</t>
   </si>
@@ -6513,6 +6513,15 @@
   </si>
   <si>
     <t>% De banco de preguntas creados por SIMA</t>
+  </si>
+  <si>
+    <t>Reducción del tiempo total de contratación</t>
+  </si>
+  <si>
+    <t>% reducción del calculo actorial - seguridad social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% de disminución de tiempos en entrega de coneptos juridicos </t>
   </si>
 </sst>
 </file>
@@ -9179,7 +9188,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>748</v>
       </c>
@@ -9202,7 +9211,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>748</v>
       </c>
@@ -9225,7 +9234,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>748</v>
       </c>
@@ -9251,7 +9260,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>748</v>
       </c>
@@ -15142,7 +15151,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1230</v>
       </c>
@@ -15155,6 +15164,9 @@
       <c r="D285" t="s">
         <v>630</v>
       </c>
+      <c r="E285" t="s">
+        <v>643</v>
+      </c>
       <c r="K285" t="s">
         <v>582</v>
       </c>
@@ -15162,7 +15174,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1230</v>
       </c>
@@ -15175,6 +15187,9 @@
       <c r="D286" t="s">
         <v>630</v>
       </c>
+      <c r="E286" t="s">
+        <v>1525</v>
+      </c>
       <c r="K286" t="s">
         <v>582</v>
       </c>
@@ -15182,7 +15197,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1230</v>
       </c>
@@ -15195,6 +15210,9 @@
       <c r="D287" t="s">
         <v>630</v>
       </c>
+      <c r="E287" t="s">
+        <v>643</v>
+      </c>
       <c r="K287" t="s">
         <v>582</v>
       </c>
@@ -15202,7 +15220,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1230</v>
       </c>
@@ -15215,6 +15233,9 @@
       <c r="D288" t="s">
         <v>630</v>
       </c>
+      <c r="E288" t="s">
+        <v>1526</v>
+      </c>
       <c r="K288" t="s">
         <v>582</v>
       </c>
@@ -15222,7 +15243,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1230</v>
       </c>
@@ -15234,6 +15255,9 @@
       </c>
       <c r="D289" t="s">
         <v>630</v>
+      </c>
+      <c r="E289" t="s">
+        <v>1527</v>
       </c>
       <c r="K289" t="s">
         <v>582</v>
@@ -15246,7 +15270,7 @@
   <autoFilter ref="A1:L289" xr:uid="{D5CC9271-A20F-4DAE-A693-53F4455B4AEF}">
     <filterColumn colId="0">
       <filters>
-        <filter val="DIRECCIÓN DE EXPERIENCIA E INCLUSIÓN"/>
+        <filter val="SECRETARIA GENERAL"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -15292,6 +15316,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E8EE7F9-C83B-46E0-BD66-45A599C1C12A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15330,7 +15355,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -15388,7 +15413,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -15417,7 +15442,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -15446,7 +15471,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -15475,7 +15500,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -15504,7 +15529,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -15533,7 +15558,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
@@ -15562,7 +15587,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -15591,7 +15616,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -15620,7 +15645,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
@@ -15649,7 +15674,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -15678,7 +15703,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
@@ -15707,7 +15732,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>59</v>
       </c>
@@ -15736,11 +15761,11 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -15765,7 +15790,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>63</v>
       </c>
@@ -15794,7 +15819,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>70</v>
       </c>
@@ -15823,7 +15848,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
@@ -15852,7 +15877,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>70</v>
       </c>
@@ -15881,7 +15906,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>70</v>
       </c>
@@ -15910,7 +15935,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>84</v>
       </c>
@@ -15939,7 +15964,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -15968,7 +15993,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>91</v>
       </c>
@@ -15997,7 +16022,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>95</v>
       </c>
@@ -16026,7 +16051,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>99</v>
       </c>
@@ -16055,7 +16080,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>99</v>
       </c>
@@ -16084,7 +16109,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>107</v>
       </c>
@@ -16113,7 +16138,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>107</v>
       </c>
@@ -16142,7 +16167,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>115</v>
       </c>
@@ -16171,7 +16196,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>119</v>
       </c>
@@ -16196,7 +16221,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>122</v>
       </c>
@@ -16225,7 +16250,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>126</v>
       </c>
@@ -16252,7 +16277,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>126</v>
       </c>
@@ -16277,7 +16302,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>130</v>
       </c>
@@ -16306,7 +16331,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="82.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>130</v>
       </c>
@@ -16335,7 +16360,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>138</v>
       </c>
@@ -16364,7 +16389,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>138</v>
       </c>
@@ -16391,7 +16416,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>144</v>
       </c>
@@ -16420,7 +16445,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>144</v>
       </c>
@@ -16449,7 +16474,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>144</v>
       </c>
@@ -16478,7 +16503,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>156</v>
       </c>
@@ -16507,7 +16532,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>161</v>
       </c>
@@ -16536,7 +16561,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>46</v>
       </c>
@@ -16565,7 +16590,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>119</v>
       </c>
@@ -16590,7 +16615,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="110.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>122</v>
       </c>
@@ -16617,7 +16642,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>144</v>
       </c>
@@ -16642,7 +16667,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>156</v>
       </c>
@@ -16668,7 +16693,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I48" xr:uid="{2E8EE7F9-C83B-46E0-BD66-45A599C1C12A}"/>
+  <autoFilter ref="A1:I48" xr:uid="{2E8EE7F9-C83B-46E0-BD66-45A599C1C12A}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="GESTIÓN JURÍDICA Y NORMATIVA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="H3">
     <cfRule type="duplicateValues" dxfId="15" priority="12"/>
   </conditionalFormatting>
@@ -17075,7 +17106,7 @@
       <c r="W6" s="25"/>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" spans="1:24" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>220</v>
       </c>
@@ -19264,7 +19295,7 @@
       <c r="W47" s="25"/>
       <c r="X47" s="25"/>
     </row>
-    <row r="48" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="64" t="s">
         <v>387</v>
       </c>
@@ -19364,7 +19395,7 @@
       <c r="W49" s="19"/>
       <c r="X49" s="19"/>
     </row>
-    <row r="50" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="64" t="s">
         <v>387</v>
       </c>
@@ -20903,7 +20934,7 @@
       <c r="F78" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="G78" s="22" t="s">
+      <c r="G78" s="59" t="s">
         <v>512</v>
       </c>
       <c r="H78" s="28" t="s">
@@ -20942,7 +20973,7 @@
       <c r="W78" s="19"/>
       <c r="X78" s="19"/>
     </row>
-    <row r="79" spans="1:24" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:24" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="72" t="s">
         <v>516</v>
       </c>
@@ -20998,7 +21029,7 @@
       <c r="W79" s="25"/>
       <c r="X79" s="25"/>
     </row>
-    <row r="80" spans="1:24" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:24" ht="70.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="72" t="s">
         <v>516</v>
       </c>
@@ -21052,7 +21083,7 @@
       <c r="W80" s="25"/>
       <c r="X80" s="25"/>
     </row>
-    <row r="81" spans="1:24" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="72" t="s">
         <v>516</v>
       </c>
@@ -21065,7 +21096,7 @@
       <c r="D81" s="73"/>
       <c r="E81" s="73"/>
       <c r="F81" s="73"/>
-      <c r="G81" s="28" t="s">
+      <c r="G81" s="93" t="s">
         <v>530</v>
       </c>
       <c r="H81" s="54" t="s">
@@ -21104,7 +21135,7 @@
       <c r="W81" s="25"/>
       <c r="X81" s="25"/>
     </row>
-    <row r="82" spans="1:24" ht="78" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="64" t="s">
         <v>516</v>
       </c>
@@ -21163,10 +21194,19 @@
       <c r="X82" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:X82" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}">
-    <filterColumn colId="10">
+  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A2:X82" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}">
+    <filterColumn colId="0">
       <filters>
-        <filter val="EXTENSIÓN"/>
+        <filter val="Factor 2. Gobierno institucional y transparencia"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <x14:filter val="Fortalecer la comunicación de los representantes a sus representados. Participación en la jornada de rendición de cuentas y demás canales institucionales_x000a__x000a_Actualizar reglamento de órganos de participación y fortalecer los mecanismos que permitan visibilizar la gestión de los diferentes grupos de interés."/>
+          </mc:Choice>
+        </mc:AlternateContent>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82ED1B49-2BC9-450F-B912-6E19EFD6CA2D}"/>
+  <xr:revisionPtr revIDLastSave="475" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B1302E5-C0DC-411D-B020-546963480EB4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Retos" sheetId="4" r:id="rId1"/>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="1528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4238" uniqueCount="1529">
   <si>
     <t>Nombre del Proyecto</t>
   </si>
@@ -6523,6 +6523,9 @@
   <si>
     <t xml:space="preserve">% de disminución de tiempos en entrega de coneptos juridicos </t>
   </si>
+  <si>
+    <t>% De aulas master creadas por SIMA</t>
+  </si>
 </sst>
 </file>
 
@@ -6533,7 +6536,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6819,6 +6822,15 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -7036,7 +7048,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7437,6 +7449,13 @@
     <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -7449,13 +7468,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -7463,7 +7476,17 @@
     <cellStyle name="Normal 2" xfId="3" xr:uid="{D9C74759-AD32-4A9C-BA5E-63E5FF0EFCF0}"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -8099,8 +8122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5CC9271-A20F-4DAE-A693-53F4455B4AEF}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:L289"/>
+  <dimension ref="A1:L290"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
@@ -8148,7 +8170,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>627</v>
       </c>
@@ -8174,7 +8196,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>627</v>
       </c>
@@ -8200,7 +8222,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>627</v>
       </c>
@@ -8229,7 +8251,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>640</v>
       </c>
@@ -8252,7 +8274,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>640</v>
       </c>
@@ -8275,7 +8297,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>647</v>
       </c>
@@ -8304,7 +8326,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>652</v>
       </c>
@@ -8330,7 +8352,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>652</v>
       </c>
@@ -8359,7 +8381,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>652</v>
       </c>
@@ -8385,7 +8407,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>652</v>
       </c>
@@ -8414,7 +8436,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>652</v>
       </c>
@@ -8437,7 +8459,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>668</v>
       </c>
@@ -8460,7 +8482,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>671</v>
       </c>
@@ -8486,7 +8508,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>671</v>
       </c>
@@ -8512,7 +8534,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>678</v>
       </c>
@@ -8535,7 +8557,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>682</v>
       </c>
@@ -8573,7 +8595,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>682</v>
       </c>
@@ -8599,7 +8621,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>682</v>
       </c>
@@ -8625,7 +8647,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>682</v>
       </c>
@@ -8654,7 +8676,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>690</v>
       </c>
@@ -8677,7 +8699,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>690</v>
       </c>
@@ -8700,7 +8722,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>695</v>
       </c>
@@ -8720,7 +8742,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>695</v>
       </c>
@@ -8746,7 +8768,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>700</v>
       </c>
@@ -8772,7 +8794,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>700</v>
       </c>
@@ -8798,7 +8820,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>700</v>
       </c>
@@ -8824,7 +8846,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>700</v>
       </c>
@@ -8850,7 +8872,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>700</v>
       </c>
@@ -8876,7 +8898,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>700</v>
       </c>
@@ -8899,7 +8921,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>716</v>
       </c>
@@ -8922,7 +8944,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>716</v>
       </c>
@@ -8943,7 +8965,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>721</v>
       </c>
@@ -8963,7 +8985,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>721</v>
       </c>
@@ -8983,7 +9005,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>721</v>
       </c>
@@ -9003,7 +9025,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>728</v>
       </c>
@@ -9032,7 +9054,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>728</v>
       </c>
@@ -9061,7 +9083,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>728</v>
       </c>
@@ -9090,7 +9112,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>728</v>
       </c>
@@ -9119,7 +9141,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>728</v>
       </c>
@@ -9148,7 +9170,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>743</v>
       </c>
@@ -9168,7 +9190,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>743</v>
       </c>
@@ -9188,7 +9210,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>748</v>
       </c>
@@ -9211,7 +9233,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>748</v>
       </c>
@@ -9234,7 +9256,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>748</v>
       </c>
@@ -9247,7 +9269,7 @@
       <c r="D45" t="s">
         <v>630</v>
       </c>
-      <c r="E45" s="146" t="s">
+      <c r="E45" s="140" t="s">
         <v>755</v>
       </c>
       <c r="G45" t="s">
@@ -9260,7 +9282,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>748</v>
       </c>
@@ -9289,7 +9311,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>760</v>
       </c>
@@ -9315,7 +9337,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>760</v>
       </c>
@@ -9341,7 +9363,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>766</v>
       </c>
@@ -9364,7 +9386,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>766</v>
       </c>
@@ -9387,7 +9409,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>766</v>
       </c>
@@ -9413,7 +9435,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>775</v>
       </c>
@@ -9442,7 +9464,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>775</v>
       </c>
@@ -9471,7 +9493,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>775</v>
       </c>
@@ -9500,7 +9522,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>775</v>
       </c>
@@ -9529,7 +9551,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>775</v>
       </c>
@@ -9558,7 +9580,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>778</v>
       </c>
@@ -9584,7 +9606,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>778</v>
       </c>
@@ -9610,7 +9632,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>778</v>
       </c>
@@ -9633,7 +9655,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>788</v>
       </c>
@@ -9659,7 +9681,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>788</v>
       </c>
@@ -9685,7 +9707,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>788</v>
       </c>
@@ -9723,7 +9745,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>788</v>
       </c>
@@ -9761,7 +9783,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>794</v>
       </c>
@@ -9781,7 +9803,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>794</v>
       </c>
@@ -9801,7 +9823,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>794</v>
       </c>
@@ -9821,7 +9843,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>801</v>
       </c>
@@ -9850,7 +9872,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>801</v>
       </c>
@@ -9879,7 +9901,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>801</v>
       </c>
@@ -9905,7 +9927,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>801</v>
       </c>
@@ -9922,7 +9944,7 @@
         <v>1524</v>
       </c>
       <c r="G70" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="K70" t="s">
         <v>587</v>
@@ -9931,7 +9953,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="71" spans="1:12" s="123" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" s="123" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="123" t="s">
         <v>811</v>
       </c>
@@ -9957,7 +9979,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>815</v>
       </c>
@@ -9983,7 +10005,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>819</v>
       </c>
@@ -10012,7 +10034,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>819</v>
       </c>
@@ -10038,7 +10060,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>819</v>
       </c>
@@ -10061,7 +10083,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>819</v>
       </c>
@@ -10087,7 +10109,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>819</v>
       </c>
@@ -10113,7 +10135,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>834</v>
       </c>
@@ -10139,7 +10161,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>834</v>
       </c>
@@ -10165,7 +10187,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>840</v>
       </c>
@@ -10191,7 +10213,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>840</v>
       </c>
@@ -10217,7 +10239,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>846</v>
       </c>
@@ -10246,7 +10268,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>846</v>
       </c>
@@ -10275,7 +10297,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>846</v>
       </c>
@@ -10304,7 +10326,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>846</v>
       </c>
@@ -10333,7 +10355,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>856</v>
       </c>
@@ -10359,7 +10381,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>856</v>
       </c>
@@ -10382,7 +10404,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>856</v>
       </c>
@@ -10405,7 +10427,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>866</v>
       </c>
@@ -10431,7 +10453,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>866</v>
       </c>
@@ -10457,7 +10479,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>866</v>
       </c>
@@ -10483,7 +10505,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>866</v>
       </c>
@@ -10506,7 +10528,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>866</v>
       </c>
@@ -10529,7 +10551,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>880</v>
       </c>
@@ -10555,7 +10577,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>880</v>
       </c>
@@ -10578,7 +10600,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>880</v>
       </c>
@@ -10601,7 +10623,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>888</v>
       </c>
@@ -10630,7 +10652,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>888</v>
       </c>
@@ -10659,7 +10681,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>888</v>
       </c>
@@ -10694,7 +10716,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>888</v>
       </c>
@@ -10723,7 +10745,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>888</v>
       </c>
@@ -10746,7 +10768,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>899</v>
       </c>
@@ -10769,7 +10791,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>899</v>
       </c>
@@ -10792,7 +10814,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>899</v>
       </c>
@@ -10818,7 +10840,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>905</v>
       </c>
@@ -10841,7 +10863,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>905</v>
       </c>
@@ -10867,7 +10889,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>905</v>
       </c>
@@ -10890,7 +10912,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>910</v>
       </c>
@@ -10916,7 +10938,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>913</v>
       </c>
@@ -10939,7 +10961,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>913</v>
       </c>
@@ -10968,7 +10990,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>913</v>
       </c>
@@ -10994,7 +11016,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>913</v>
       </c>
@@ -11017,7 +11039,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>913</v>
       </c>
@@ -11040,7 +11062,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>913</v>
       </c>
@@ -11063,7 +11085,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>913</v>
       </c>
@@ -11086,7 +11108,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>913</v>
       </c>
@@ -11109,7 +11131,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>936</v>
       </c>
@@ -11132,7 +11154,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>936</v>
       </c>
@@ -11155,7 +11177,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>936</v>
       </c>
@@ -11184,7 +11206,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>936</v>
       </c>
@@ -11213,7 +11235,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>948</v>
       </c>
@@ -11236,7 +11258,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>948</v>
       </c>
@@ -11259,7 +11281,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>948</v>
       </c>
@@ -11288,7 +11310,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>948</v>
       </c>
@@ -11317,7 +11339,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>955</v>
       </c>
@@ -11340,7 +11362,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>955</v>
       </c>
@@ -11363,7 +11385,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>955</v>
       </c>
@@ -11392,7 +11414,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>955</v>
       </c>
@@ -11415,7 +11437,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>964</v>
       </c>
@@ -11438,7 +11460,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>964</v>
       </c>
@@ -11461,7 +11483,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>964</v>
       </c>
@@ -11490,7 +11512,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>964</v>
       </c>
@@ -11519,7 +11541,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>971</v>
       </c>
@@ -11542,7 +11564,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>971</v>
       </c>
@@ -11565,7 +11587,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>971</v>
       </c>
@@ -11588,7 +11610,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>971</v>
       </c>
@@ -11617,7 +11639,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>971</v>
       </c>
@@ -11646,7 +11668,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>980</v>
       </c>
@@ -11669,7 +11691,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>980</v>
       </c>
@@ -11692,7 +11714,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>980</v>
       </c>
@@ -11715,7 +11737,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>980</v>
       </c>
@@ -11738,7 +11760,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>980</v>
       </c>
@@ -11767,7 +11789,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>980</v>
       </c>
@@ -11790,7 +11812,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>992</v>
       </c>
@@ -11813,7 +11835,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>992</v>
       </c>
@@ -11836,7 +11858,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>992</v>
       </c>
@@ -11865,7 +11887,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>992</v>
       </c>
@@ -11894,7 +11916,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>998</v>
       </c>
@@ -11917,7 +11939,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>998</v>
       </c>
@@ -11940,7 +11962,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>998</v>
       </c>
@@ -11966,7 +11988,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>998</v>
       </c>
@@ -11989,7 +12011,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>998</v>
       </c>
@@ -12015,7 +12037,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>998</v>
       </c>
@@ -12038,7 +12060,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>998</v>
       </c>
@@ -12061,7 +12083,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>1016</v>
       </c>
@@ -12084,7 +12106,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>1016</v>
       </c>
@@ -12107,7 +12129,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>1016</v>
       </c>
@@ -12136,7 +12158,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>1016</v>
       </c>
@@ -12165,7 +12187,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>1025</v>
       </c>
@@ -12188,7 +12210,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>1025</v>
       </c>
@@ -12211,7 +12233,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>1025</v>
       </c>
@@ -12240,7 +12262,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>1025</v>
       </c>
@@ -12269,7 +12291,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>1025</v>
       </c>
@@ -12292,7 +12314,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>1034</v>
       </c>
@@ -12315,7 +12337,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>1034</v>
       </c>
@@ -12338,7 +12360,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>1034</v>
       </c>
@@ -12367,7 +12389,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>1034</v>
       </c>
@@ -12396,7 +12418,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>1037</v>
       </c>
@@ -12419,7 +12441,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>1037</v>
       </c>
@@ -12442,7 +12464,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>1037</v>
       </c>
@@ -12471,7 +12493,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>1037</v>
       </c>
@@ -12500,7 +12522,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1044</v>
       </c>
@@ -12520,7 +12542,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>1044</v>
       </c>
@@ -12540,7 +12562,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>1044</v>
       </c>
@@ -12560,7 +12582,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>1050</v>
       </c>
@@ -12583,7 +12605,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>1050</v>
       </c>
@@ -12606,7 +12628,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>1050</v>
       </c>
@@ -12635,7 +12657,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>1050</v>
       </c>
@@ -12664,7 +12686,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>1056</v>
       </c>
@@ -12687,7 +12709,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>1056</v>
       </c>
@@ -12716,7 +12738,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>1056</v>
       </c>
@@ -12739,7 +12761,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>1056</v>
       </c>
@@ -12768,7 +12790,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>1060</v>
       </c>
@@ -12791,7 +12813,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>1060</v>
       </c>
@@ -12814,7 +12836,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>1060</v>
       </c>
@@ -12843,7 +12865,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>1060</v>
       </c>
@@ -12872,7 +12894,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>1066</v>
       </c>
@@ -12895,7 +12917,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>1066</v>
       </c>
@@ -12921,7 +12943,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>1066</v>
       </c>
@@ -12944,7 +12966,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>1066</v>
       </c>
@@ -12973,7 +12995,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>1071</v>
       </c>
@@ -12996,7 +13018,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>1071</v>
       </c>
@@ -13020,7 +13042,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1071</v>
       </c>
@@ -13040,7 +13062,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1071</v>
       </c>
@@ -13060,7 +13082,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1071</v>
       </c>
@@ -13080,7 +13102,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>1071</v>
       </c>
@@ -13103,7 +13125,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1071</v>
       </c>
@@ -13123,7 +13145,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1071</v>
       </c>
@@ -13146,7 +13168,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1071</v>
       </c>
@@ -13169,7 +13191,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>1071</v>
       </c>
@@ -13189,7 +13211,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1071</v>
       </c>
@@ -13212,7 +13234,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1071</v>
       </c>
@@ -13238,7 +13260,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1071</v>
       </c>
@@ -13258,7 +13280,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1071</v>
       </c>
@@ -13287,7 +13309,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1102</v>
       </c>
@@ -13307,7 +13329,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1102</v>
       </c>
@@ -13327,7 +13349,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1106</v>
       </c>
@@ -13347,7 +13369,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1106</v>
       </c>
@@ -13367,7 +13389,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>1106</v>
       </c>
@@ -13387,7 +13409,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>1106</v>
       </c>
@@ -13407,7 +13429,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>1106</v>
       </c>
@@ -13427,7 +13449,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>1106</v>
       </c>
@@ -13447,7 +13469,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>1106</v>
       </c>
@@ -13467,7 +13489,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>1106</v>
       </c>
@@ -13487,7 +13509,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>1106</v>
       </c>
@@ -13507,7 +13529,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>1123</v>
       </c>
@@ -13530,7 +13552,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>1123</v>
       </c>
@@ -13553,7 +13575,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>1123</v>
       </c>
@@ -13582,7 +13604,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>1123</v>
       </c>
@@ -13611,7 +13633,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>1131</v>
       </c>
@@ -13634,7 +13656,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>1131</v>
       </c>
@@ -13657,7 +13679,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>1131</v>
       </c>
@@ -13686,7 +13708,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>1131</v>
       </c>
@@ -13709,7 +13731,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>1131</v>
       </c>
@@ -13738,7 +13760,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>1138</v>
       </c>
@@ -13758,7 +13780,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1138</v>
       </c>
@@ -13778,7 +13800,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>1138</v>
       </c>
@@ -13798,7 +13820,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1138</v>
       </c>
@@ -13818,7 +13840,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>1142</v>
       </c>
@@ -13838,7 +13860,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>1144</v>
       </c>
@@ -13858,7 +13880,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1145</v>
       </c>
@@ -13878,7 +13900,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1145</v>
       </c>
@@ -13898,7 +13920,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1145</v>
       </c>
@@ -13918,7 +13940,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>1145</v>
       </c>
@@ -13938,7 +13960,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1149</v>
       </c>
@@ -13958,7 +13980,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1149</v>
       </c>
@@ -13978,7 +14000,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1149</v>
       </c>
@@ -13998,7 +14020,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1149</v>
       </c>
@@ -14018,7 +14040,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1152</v>
       </c>
@@ -14047,7 +14069,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1157</v>
       </c>
@@ -14076,7 +14098,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1157</v>
       </c>
@@ -14105,7 +14127,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1157</v>
       </c>
@@ -14134,7 +14156,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1157</v>
       </c>
@@ -14163,7 +14185,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1157</v>
       </c>
@@ -14195,7 +14217,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1157</v>
       </c>
@@ -14224,7 +14246,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1157</v>
       </c>
@@ -14253,7 +14275,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1168</v>
       </c>
@@ -14273,7 +14295,7 @@
         <v>0.82</v>
       </c>
       <c r="G247" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="K247" t="s">
         <v>587</v>
@@ -14282,7 +14304,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1168</v>
       </c>
@@ -14301,6 +14323,9 @@
       <c r="F248" s="121">
         <v>1</v>
       </c>
+      <c r="G248" t="s">
+        <v>639</v>
+      </c>
       <c r="K248" t="s">
         <v>587</v>
       </c>
@@ -14308,7 +14333,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="249" spans="1:12" s="123" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" s="123" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A249" s="123" t="s">
         <v>1168</v>
       </c>
@@ -14321,20 +14346,20 @@
       <c r="D249" s="123" t="s">
         <v>630</v>
       </c>
-      <c r="E249" s="123" t="s">
+      <c r="E249" s="147" t="s">
         <v>883</v>
       </c>
-      <c r="G249" s="123" t="s">
-        <v>632</v>
+      <c r="G249" t="s">
+        <v>639</v>
       </c>
       <c r="K249" s="123" t="s">
-        <v>587</v>
-      </c>
-      <c r="L249" s="123" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+      <c r="L249" s="6" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1168</v>
       </c>
@@ -14351,7 +14376,7 @@
         <v>885</v>
       </c>
       <c r="G250" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="K250" t="s">
         <v>587</v>
@@ -14360,7 +14385,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1168</v>
       </c>
@@ -14376,6 +14401,9 @@
       <c r="E251" t="s">
         <v>887</v>
       </c>
+      <c r="G251" t="s">
+        <v>639</v>
+      </c>
       <c r="K251" t="s">
         <v>587</v>
       </c>
@@ -14383,7 +14411,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1168</v>
       </c>
@@ -14397,7 +14425,7 @@
         <v>630</v>
       </c>
       <c r="E252" s="8" t="s">
-        <v>810</v>
+        <v>1528</v>
       </c>
       <c r="G252" t="s">
         <v>632</v>
@@ -14409,7 +14437,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1175</v>
       </c>
@@ -14429,7 +14457,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1177</v>
       </c>
@@ -14449,7 +14477,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1177</v>
       </c>
@@ -14469,7 +14497,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1177</v>
       </c>
@@ -14489,7 +14517,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1184</v>
       </c>
@@ -14509,7 +14537,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1184</v>
       </c>
@@ -14529,7 +14557,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1188</v>
       </c>
@@ -14549,7 +14577,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1188</v>
       </c>
@@ -14569,7 +14597,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1192</v>
       </c>
@@ -14589,7 +14617,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1192</v>
       </c>
@@ -14609,7 +14637,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1193</v>
       </c>
@@ -14635,7 +14663,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1193</v>
       </c>
@@ -14661,7 +14689,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1193</v>
       </c>
@@ -14687,7 +14715,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1193</v>
       </c>
@@ -14713,7 +14741,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1193</v>
       </c>
@@ -14739,7 +14767,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1196</v>
       </c>
@@ -14765,7 +14793,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1200</v>
       </c>
@@ -14785,7 +14813,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1200</v>
       </c>
@@ -14805,7 +14833,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1204</v>
       </c>
@@ -14834,7 +14862,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1204</v>
       </c>
@@ -14863,7 +14891,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1204</v>
       </c>
@@ -14892,7 +14920,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1204</v>
       </c>
@@ -14921,7 +14949,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1204</v>
       </c>
@@ -14950,7 +14978,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1206</v>
       </c>
@@ -14970,7 +14998,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1207</v>
       </c>
@@ -14996,7 +15024,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1211</v>
       </c>
@@ -15019,7 +15047,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1215</v>
       </c>
@@ -15039,7 +15067,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1215</v>
       </c>
@@ -15059,7 +15087,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1215</v>
       </c>
@@ -15079,7 +15107,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1222</v>
       </c>
@@ -15102,7 +15130,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1222</v>
       </c>
@@ -15125,7 +15153,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1222</v>
       </c>
@@ -15266,48 +15294,70 @@
         <v>582</v>
       </c>
     </row>
+    <row r="290" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B290" t="s">
+        <v>808</v>
+      </c>
+      <c r="C290" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D290" t="s">
+        <v>630</v>
+      </c>
+      <c r="E290" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="G290" t="s">
+        <v>639</v>
+      </c>
+      <c r="K290" t="s">
+        <v>587</v>
+      </c>
+      <c r="L290" t="s">
+        <v>603</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L289" xr:uid="{D5CC9271-A20F-4DAE-A693-53F4455B4AEF}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="SECRETARIA GENERAL"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L4">
-    <cfRule type="duplicateValues" dxfId="26" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8:L12">
-    <cfRule type="duplicateValues" dxfId="25" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L16">
-    <cfRule type="duplicateValues" dxfId="24" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L64:L66">
-    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L88">
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L97:L101">
-    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L106">
-    <cfRule type="duplicateValues" dxfId="20" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L163">
-    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L241">
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L242">
     <cfRule type="duplicateValues" dxfId="18" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L242">
+  <conditionalFormatting sqref="L268">
     <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L268">
+  <conditionalFormatting sqref="L249">
     <cfRule type="duplicateValues" dxfId="16" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16733,7 +16783,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:X82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16768,15 +16817,15 @@
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
       <c r="Q1"/>
-      <c r="R1" s="142" t="s">
+      <c r="R1" s="145" t="s">
         <v>174</v>
       </c>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="146"/>
+      <c r="U1" s="146"/>
+      <c r="V1" s="146"/>
+      <c r="W1" s="146"/>
+      <c r="X1" s="146"/>
     </row>
     <row r="2" spans="1:24" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -16852,7 +16901,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="202.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="202.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>189</v>
       </c>
@@ -16922,7 +16971,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="171.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>189</v>
       </c>
@@ -16990,7 +17039,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>189</v>
       </c>
@@ -17048,7 +17097,7 @@
       <c r="W5" s="25"/>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" spans="1:24" ht="69" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>189</v>
       </c>
@@ -17166,7 +17215,7 @@
       <c r="W7" s="36"/>
       <c r="X7" s="36"/>
     </row>
-    <row r="8" spans="1:24" ht="202.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="202.8" x14ac:dyDescent="0.3">
       <c r="A8" s="29" t="s">
         <v>220</v>
       </c>
@@ -17218,7 +17267,7 @@
       <c r="W8" s="36"/>
       <c r="X8" s="36"/>
     </row>
-    <row r="9" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A9" s="29" t="s">
         <v>220</v>
       </c>
@@ -17264,7 +17313,7 @@
       <c r="W9" s="36"/>
       <c r="X9" s="36"/>
     </row>
-    <row r="10" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A10" s="29" t="s">
         <v>220</v>
       </c>
@@ -17329,7 +17378,7 @@
       <c r="W10" s="36"/>
       <c r="X10" s="36"/>
     </row>
-    <row r="11" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="29" t="s">
         <v>220</v>
       </c>
@@ -17391,7 +17440,7 @@
       <c r="W11" s="36"/>
       <c r="X11" s="36"/>
     </row>
-    <row r="12" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="29" t="s">
         <v>220</v>
       </c>
@@ -17449,7 +17498,7 @@
       <c r="W12" s="36"/>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="1:24" ht="50.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" ht="50.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
         <v>248</v>
       </c>
@@ -17499,7 +17548,7 @@
       <c r="W13" s="25"/>
       <c r="X13" s="25"/>
     </row>
-    <row r="14" spans="1:24" ht="49.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
         <v>248</v>
       </c>
@@ -17549,7 +17598,7 @@
       <c r="W14" s="25"/>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="28" t="s">
         <v>248</v>
       </c>
@@ -17589,21 +17638,21 @@
       <c r="M15" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N15" s="144"/>
-      <c r="O15" s="144"/>
-      <c r="P15" s="140" t="s">
+      <c r="N15" s="141"/>
+      <c r="O15" s="141"/>
+      <c r="P15" s="143" t="s">
         <v>263</v>
       </c>
-      <c r="Q15" s="140"/>
-      <c r="R15" s="140"/>
-      <c r="S15" s="140"/>
-      <c r="T15" s="140"/>
-      <c r="U15" s="140"/>
-      <c r="V15" s="140"/>
-      <c r="W15" s="140"/>
-      <c r="X15" s="140"/>
-    </row>
-    <row r="16" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q15" s="143"/>
+      <c r="R15" s="143"/>
+      <c r="S15" s="143"/>
+      <c r="T15" s="143"/>
+      <c r="U15" s="143"/>
+      <c r="V15" s="143"/>
+      <c r="W15" s="143"/>
+      <c r="X15" s="143"/>
+    </row>
+    <row r="16" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
         <v>248</v>
       </c>
@@ -17643,19 +17692,19 @@
       <c r="M16" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N16" s="145"/>
-      <c r="O16" s="145"/>
-      <c r="P16" s="141"/>
-      <c r="Q16" s="141"/>
-      <c r="R16" s="141"/>
-      <c r="S16" s="141"/>
-      <c r="T16" s="141"/>
-      <c r="U16" s="141"/>
-      <c r="V16" s="141"/>
-      <c r="W16" s="141"/>
-      <c r="X16" s="141"/>
-    </row>
-    <row r="17" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="142"/>
+      <c r="O16" s="142"/>
+      <c r="P16" s="144"/>
+      <c r="Q16" s="144"/>
+      <c r="R16" s="144"/>
+      <c r="S16" s="144"/>
+      <c r="T16" s="144"/>
+      <c r="U16" s="144"/>
+      <c r="V16" s="144"/>
+      <c r="W16" s="144"/>
+      <c r="X16" s="144"/>
+    </row>
+    <row r="17" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
         <v>248</v>
       </c>
@@ -17709,7 +17758,7 @@
       <c r="W17" s="19"/>
       <c r="X17" s="19"/>
     </row>
-    <row r="18" spans="1:24" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>248</v>
       </c>
@@ -17759,7 +17808,7 @@
       <c r="W18" s="25"/>
       <c r="X18" s="25"/>
     </row>
-    <row r="19" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
         <v>248</v>
       </c>
@@ -17809,7 +17858,7 @@
       <c r="W19" s="19"/>
       <c r="X19" s="19"/>
     </row>
-    <row r="20" spans="1:24" ht="31.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="28" t="s">
         <v>248</v>
       </c>
@@ -17857,7 +17906,7 @@
       <c r="W20" s="25"/>
       <c r="X20" s="25"/>
     </row>
-    <row r="21" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A21" s="28" t="s">
         <v>248</v>
       </c>
@@ -17905,7 +17954,7 @@
       <c r="W21" s="25"/>
       <c r="X21" s="25"/>
     </row>
-    <row r="22" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A22" s="28" t="s">
         <v>248</v>
       </c>
@@ -17955,7 +18004,7 @@
       <c r="W22" s="19"/>
       <c r="X22" s="19"/>
     </row>
-    <row r="23" spans="1:24" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A23" s="28" t="s">
         <v>248</v>
       </c>
@@ -18009,7 +18058,7 @@
       <c r="W23" s="25"/>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" spans="1:24" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A24" s="61" t="s">
         <v>289</v>
       </c>
@@ -18061,7 +18110,7 @@
       <c r="W24" s="19"/>
       <c r="X24" s="19"/>
     </row>
-    <row r="25" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A25" s="61" t="s">
         <v>289</v>
       </c>
@@ -18117,7 +18166,7 @@
       <c r="W25" s="19"/>
       <c r="X25" s="19"/>
     </row>
-    <row r="26" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A26" s="61" t="s">
         <v>289</v>
       </c>
@@ -18171,7 +18220,7 @@
       <c r="W26" s="19"/>
       <c r="X26" s="19"/>
     </row>
-    <row r="27" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A27" s="61" t="s">
         <v>289</v>
       </c>
@@ -18231,7 +18280,7 @@
       <c r="W27" s="19"/>
       <c r="X27" s="19"/>
     </row>
-    <row r="28" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A28" s="61" t="s">
         <v>289</v>
       </c>
@@ -18291,7 +18340,7 @@
       <c r="W28" s="19"/>
       <c r="X28" s="19"/>
     </row>
-    <row r="29" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A29" s="61" t="s">
         <v>289</v>
       </c>
@@ -18349,7 +18398,7 @@
       <c r="W29" s="19"/>
       <c r="X29" s="19"/>
     </row>
-    <row r="30" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A30" s="61" t="s">
         <v>289</v>
       </c>
@@ -18405,7 +18454,7 @@
       <c r="W30" s="19"/>
       <c r="X30" s="19"/>
     </row>
-    <row r="31" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A31" s="61" t="s">
         <v>289</v>
       </c>
@@ -18465,7 +18514,7 @@
       <c r="W31" s="19"/>
       <c r="X31" s="19"/>
     </row>
-    <row r="32" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A32" s="61" t="s">
         <v>289</v>
       </c>
@@ -18523,7 +18572,7 @@
       <c r="W32" s="19"/>
       <c r="X32" s="19"/>
     </row>
-    <row r="33" spans="1:24" ht="31.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="61" t="s">
         <v>289</v>
       </c>
@@ -18567,7 +18616,7 @@
       <c r="W33" s="25"/>
       <c r="X33" s="25"/>
     </row>
-    <row r="34" spans="1:24" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="49" t="s">
         <v>341</v>
       </c>
@@ -18619,7 +18668,7 @@
       <c r="W34" s="25"/>
       <c r="X34" s="25"/>
     </row>
-    <row r="35" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A35" s="49" t="s">
         <v>341</v>
       </c>
@@ -18667,7 +18716,7 @@
       <c r="W35" s="25"/>
       <c r="X35" s="25"/>
     </row>
-    <row r="36" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A36" s="61" t="s">
         <v>341</v>
       </c>
@@ -18725,7 +18774,7 @@
       <c r="W36" s="19"/>
       <c r="X36" s="19"/>
     </row>
-    <row r="37" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A37" s="49" t="s">
         <v>341</v>
       </c>
@@ -18773,7 +18822,7 @@
       <c r="W37" s="25"/>
       <c r="X37" s="25"/>
     </row>
-    <row r="38" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A38" s="61" t="s">
         <v>341</v>
       </c>
@@ -18825,7 +18874,7 @@
       <c r="W38" s="19"/>
       <c r="X38" s="19"/>
     </row>
-    <row r="39" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A39" s="61" t="s">
         <v>341</v>
       </c>
@@ -18873,7 +18922,7 @@
       <c r="W39" s="19"/>
       <c r="X39" s="19"/>
     </row>
-    <row r="40" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A40" s="61" t="s">
         <v>341</v>
       </c>
@@ -18923,7 +18972,7 @@
       <c r="W40" s="78"/>
       <c r="X40" s="78"/>
     </row>
-    <row r="41" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A41" s="30" t="s">
         <v>369</v>
       </c>
@@ -18983,7 +19032,7 @@
       <c r="W41" s="36"/>
       <c r="X41" s="36"/>
     </row>
-    <row r="42" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A42" s="30" t="s">
         <v>369</v>
       </c>
@@ -19037,7 +19086,7 @@
       <c r="W42" s="36"/>
       <c r="X42" s="36"/>
     </row>
-    <row r="43" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A43" s="30" t="s">
         <v>369</v>
       </c>
@@ -19091,7 +19140,7 @@
       <c r="W43" s="36"/>
       <c r="X43" s="36"/>
     </row>
-    <row r="44" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A44" s="30" t="s">
         <v>369</v>
       </c>
@@ -19139,7 +19188,7 @@
       <c r="W44" s="36"/>
       <c r="X44" s="36"/>
     </row>
-    <row r="45" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A45" s="30" t="s">
         <v>369</v>
       </c>
@@ -19195,7 +19244,7 @@
       <c r="W45" s="36"/>
       <c r="X45" s="36"/>
     </row>
-    <row r="46" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A46" s="30" t="s">
         <v>369</v>
       </c>
@@ -19247,7 +19296,7 @@
       <c r="W46" s="36"/>
       <c r="X46" s="36"/>
     </row>
-    <row r="47" spans="1:24" ht="31.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="72" t="s">
         <v>387</v>
       </c>
@@ -19295,7 +19344,7 @@
       <c r="W47" s="25"/>
       <c r="X47" s="25"/>
     </row>
-    <row r="48" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A48" s="64" t="s">
         <v>387</v>
       </c>
@@ -19345,7 +19394,7 @@
       <c r="W48" s="19"/>
       <c r="X48" s="19"/>
     </row>
-    <row r="49" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A49" s="64" t="s">
         <v>387</v>
       </c>
@@ -19395,7 +19444,7 @@
       <c r="W49" s="19"/>
       <c r="X49" s="19"/>
     </row>
-    <row r="50" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A50" s="64" t="s">
         <v>387</v>
       </c>
@@ -19441,7 +19490,7 @@
       <c r="W50" s="19"/>
       <c r="X50" s="19"/>
     </row>
-    <row r="51" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A51" s="64" t="s">
         <v>387</v>
       </c>
@@ -19493,7 +19542,7 @@
       <c r="W51" s="19"/>
       <c r="X51" s="19"/>
     </row>
-    <row r="52" spans="1:24" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72" t="s">
         <v>408</v>
       </c>
@@ -19547,7 +19596,7 @@
       <c r="W52" s="25"/>
       <c r="X52" s="25"/>
     </row>
-    <row r="53" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A53" s="72" t="s">
         <v>408</v>
       </c>
@@ -19597,7 +19646,7 @@
       <c r="W53" s="19"/>
       <c r="X53" s="19"/>
     </row>
-    <row r="54" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A54" s="72" t="s">
         <v>408</v>
       </c>
@@ -19653,7 +19702,7 @@
       <c r="W54" s="19"/>
       <c r="X54" s="19"/>
     </row>
-    <row r="55" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A55" s="72" t="s">
         <v>408</v>
       </c>
@@ -19711,7 +19760,7 @@
       <c r="W55" s="19"/>
       <c r="X55" s="19"/>
     </row>
-    <row r="56" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A56" s="72" t="s">
         <v>408</v>
       </c>
@@ -19769,7 +19818,7 @@
       <c r="W56" s="19"/>
       <c r="X56" s="19"/>
     </row>
-    <row r="57" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A57" s="72" t="s">
         <v>408</v>
       </c>
@@ -19827,7 +19876,7 @@
       <c r="W57" s="19"/>
       <c r="X57" s="19"/>
     </row>
-    <row r="58" spans="1:24" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="72" t="s">
         <v>433</v>
       </c>
@@ -19881,7 +19930,7 @@
       <c r="W58" s="25"/>
       <c r="X58" s="25"/>
     </row>
-    <row r="59" spans="1:24" ht="76.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" ht="76.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="64" t="s">
         <v>433</v>
       </c>
@@ -19931,7 +19980,7 @@
       <c r="W59" s="19"/>
       <c r="X59" s="19"/>
     </row>
-    <row r="60" spans="1:24" ht="67.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="72" t="s">
         <v>433</v>
       </c>
@@ -19977,7 +20026,7 @@
       <c r="W60" s="25"/>
       <c r="X60" s="25"/>
     </row>
-    <row r="61" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A61" s="64" t="s">
         <v>433</v>
       </c>
@@ -20027,7 +20076,7 @@
       <c r="W61" s="19"/>
       <c r="X61" s="19"/>
     </row>
-    <row r="62" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A62" s="64" t="s">
         <v>448</v>
       </c>
@@ -20081,7 +20130,7 @@
       <c r="W62" s="19"/>
       <c r="X62" s="19"/>
     </row>
-    <row r="63" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A63" s="64" t="s">
         <v>448</v>
       </c>
@@ -20135,7 +20184,7 @@
       <c r="W63" s="19"/>
       <c r="X63" s="19"/>
     </row>
-    <row r="64" spans="1:24" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="72" t="s">
         <v>448</v>
       </c>
@@ -20181,7 +20230,7 @@
       <c r="W64" s="25"/>
       <c r="X64" s="25"/>
     </row>
-    <row r="65" spans="1:24" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:24" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="72" t="s">
         <v>448</v>
       </c>
@@ -20237,7 +20286,7 @@
       <c r="W65" s="25"/>
       <c r="X65" s="25"/>
     </row>
-    <row r="66" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A66" s="64" t="s">
         <v>448</v>
       </c>
@@ -20297,7 +20346,7 @@
       <c r="W66" s="19"/>
       <c r="X66" s="19"/>
     </row>
-    <row r="67" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A67" s="64" t="s">
         <v>448</v>
       </c>
@@ -20367,7 +20416,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="68" spans="1:24" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A68" s="64" t="s">
         <v>448</v>
       </c>
@@ -20431,7 +20480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:24" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:24" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A69" s="64" t="s">
         <v>448</v>
       </c>
@@ -20485,7 +20534,7 @@
       <c r="W69" s="19"/>
       <c r="X69" s="19"/>
     </row>
-    <row r="70" spans="1:24" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:24" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A70" s="64" t="s">
         <v>448</v>
       </c>
@@ -20539,7 +20588,7 @@
       <c r="W70" s="19"/>
       <c r="X70" s="19"/>
     </row>
-    <row r="71" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A71" s="64" t="s">
         <v>486</v>
       </c>
@@ -20589,7 +20638,7 @@
       <c r="W71" s="19"/>
       <c r="X71" s="19"/>
     </row>
-    <row r="72" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A72" s="64" t="s">
         <v>486</v>
       </c>
@@ -20637,7 +20686,7 @@
       <c r="W72" s="19"/>
       <c r="X72" s="19"/>
     </row>
-    <row r="73" spans="1:24" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:24" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A73" s="64" t="s">
         <v>486</v>
       </c>
@@ -20689,7 +20738,7 @@
       <c r="W73" s="19"/>
       <c r="X73" s="19"/>
     </row>
-    <row r="74" spans="1:24" ht="156" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:24" ht="156" x14ac:dyDescent="0.3">
       <c r="A74" s="64" t="s">
         <v>486</v>
       </c>
@@ -20747,7 +20796,7 @@
       <c r="W74" s="19"/>
       <c r="X74" s="19"/>
     </row>
-    <row r="75" spans="1:24" ht="156" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:24" ht="156" x14ac:dyDescent="0.3">
       <c r="A75" s="64" t="s">
         <v>486</v>
       </c>
@@ -20805,7 +20854,7 @@
       <c r="W75" s="19"/>
       <c r="X75" s="19"/>
     </row>
-    <row r="76" spans="1:24" ht="124.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:24" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="72" t="s">
         <v>486</v>
       </c>
@@ -20861,7 +20910,7 @@
       <c r="W76" s="25"/>
       <c r="X76" s="25"/>
     </row>
-    <row r="77" spans="1:24" ht="156" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:24" ht="156" x14ac:dyDescent="0.3">
       <c r="A77" s="64" t="s">
         <v>486</v>
       </c>
@@ -20915,7 +20964,7 @@
       <c r="W77" s="19"/>
       <c r="X77" s="19"/>
     </row>
-    <row r="78" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A78" s="64" t="s">
         <v>486</v>
       </c>
@@ -20973,7 +21022,7 @@
       <c r="W78" s="19"/>
       <c r="X78" s="19"/>
     </row>
-    <row r="79" spans="1:24" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:24" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A79" s="72" t="s">
         <v>516</v>
       </c>
@@ -21029,7 +21078,7 @@
       <c r="W79" s="25"/>
       <c r="X79" s="25"/>
     </row>
-    <row r="80" spans="1:24" ht="70.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:24" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="72" t="s">
         <v>516</v>
       </c>
@@ -21083,7 +21132,7 @@
       <c r="W80" s="25"/>
       <c r="X80" s="25"/>
     </row>
-    <row r="81" spans="1:24" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A81" s="72" t="s">
         <v>516</v>
       </c>
@@ -21135,7 +21184,7 @@
       <c r="W81" s="25"/>
       <c r="X81" s="25"/>
     </row>
-    <row r="82" spans="1:24" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24" ht="78" x14ac:dyDescent="0.3">
       <c r="A82" s="64" t="s">
         <v>516</v>
       </c>
@@ -21194,28 +21243,8 @@
       <c r="X82" s="19"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A2:X82" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Factor 2. Gobierno institucional y transparencia"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <x14:filter val="Fortalecer la comunicación de los representantes a sus representados. Participación en la jornada de rendición de cuentas y demás canales institucionales_x000a__x000a_Actualizar reglamento de órganos de participación y fortalecer los mecanismos que permitan visibilizar la gestión de los diferentes grupos de interés."/>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:X82" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}"/>
   <mergeCells count="12">
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
     <mergeCell ref="V15:V16"/>
     <mergeCell ref="W15:W16"/>
     <mergeCell ref="X15:X16"/>
@@ -21223,6 +21252,11 @@
     <mergeCell ref="S15:S16"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="U15:U16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="475" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B1302E5-C0DC-411D-B020-546963480EB4}"/>
+  <xr:revisionPtr revIDLastSave="479" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ACC6CE6-ACA8-4B91-8D38-8C118E415600}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan de mejoramiento'!$A$2:$X$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Proceso!$A$1:$D$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Proyectos!$A$1:$I$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Retos!$A$1:$L$289</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Retos!$A$1:$L$290</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -7450,12 +7450,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -7468,7 +7463,12 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -9901,7 +9901,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>801</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>801</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>888</v>
       </c>
@@ -10912,7 +10912,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>910</v>
       </c>
@@ -11016,7 +11016,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>913</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>998</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1152</v>
       </c>
@@ -14346,7 +14346,7 @@
       <c r="D249" s="123" t="s">
         <v>630</v>
       </c>
-      <c r="E249" s="147" t="s">
+      <c r="E249" s="141" t="s">
         <v>883</v>
       </c>
       <c r="G249" t="s">
@@ -14376,7 +14376,7 @@
         <v>885</v>
       </c>
       <c r="G250" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="K250" t="s">
         <v>587</v>
@@ -15294,7 +15294,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1168</v>
       </c>
@@ -15354,11 +15354,11 @@
   <conditionalFormatting sqref="L242">
     <cfRule type="duplicateValues" dxfId="18" priority="3"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L249">
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L268">
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L249">
-    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16817,15 +16817,15 @@
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
       <c r="Q1"/>
-      <c r="R1" s="145" t="s">
+      <c r="R1" s="144" t="s">
         <v>174</v>
       </c>
-      <c r="S1" s="146"/>
-      <c r="T1" s="146"/>
-      <c r="U1" s="146"/>
-      <c r="V1" s="146"/>
-      <c r="W1" s="146"/>
-      <c r="X1" s="146"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
     </row>
     <row r="2" spans="1:24" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -17638,19 +17638,19 @@
       <c r="M15" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N15" s="141"/>
-      <c r="O15" s="141"/>
-      <c r="P15" s="143" t="s">
+      <c r="N15" s="146"/>
+      <c r="O15" s="146"/>
+      <c r="P15" s="142" t="s">
         <v>263</v>
       </c>
-      <c r="Q15" s="143"/>
-      <c r="R15" s="143"/>
-      <c r="S15" s="143"/>
-      <c r="T15" s="143"/>
-      <c r="U15" s="143"/>
-      <c r="V15" s="143"/>
-      <c r="W15" s="143"/>
-      <c r="X15" s="143"/>
+      <c r="Q15" s="142"/>
+      <c r="R15" s="142"/>
+      <c r="S15" s="142"/>
+      <c r="T15" s="142"/>
+      <c r="U15" s="142"/>
+      <c r="V15" s="142"/>
+      <c r="W15" s="142"/>
+      <c r="X15" s="142"/>
     </row>
     <row r="16" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
@@ -17692,17 +17692,17 @@
       <c r="M16" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="N16" s="142"/>
-      <c r="O16" s="142"/>
-      <c r="P16" s="144"/>
-      <c r="Q16" s="144"/>
-      <c r="R16" s="144"/>
-      <c r="S16" s="144"/>
-      <c r="T16" s="144"/>
-      <c r="U16" s="144"/>
-      <c r="V16" s="144"/>
-      <c r="W16" s="144"/>
-      <c r="X16" s="144"/>
+      <c r="N16" s="147"/>
+      <c r="O16" s="147"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="143"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="143"/>
+      <c r="T16" s="143"/>
+      <c r="U16" s="143"/>
+      <c r="V16" s="143"/>
+      <c r="W16" s="143"/>
+      <c r="X16" s="143"/>
     </row>
     <row r="17" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
@@ -21245,6 +21245,11 @@
   </sheetData>
   <autoFilter ref="A2:X82" xr:uid="{FE13F4EE-2FD9-468D-B5E2-4C4E3F15541D}"/>
   <mergeCells count="12">
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
     <mergeCell ref="V15:V16"/>
     <mergeCell ref="W15:W16"/>
     <mergeCell ref="X15:X16"/>
@@ -21252,11 +21257,6 @@
     <mergeCell ref="S15:S16"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="U15:U16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
+++ b/data/raw/Propuesta Indicadores/Indicadores Propuestos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Propuesta Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="479" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ACC6CE6-ACA8-4B91-8D38-8C118E415600}"/>
+  <xr:revisionPtr revIDLastSave="485" documentId="8_{1EE08A9A-8718-4E10-AA8A-F93130741B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB9E43BD-387B-4110-AA9A-7149240CEA2E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B9AA2411-AA05-4D1A-A9B2-553D70C050E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Retos" sheetId="4" r:id="rId1"/>
@@ -15366,7 +15366,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E8EE7F9-C83B-46E0-BD66-45A599C1C12A}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15405,7 +15404,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -15463,7 +15462,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -15492,7 +15491,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -15521,7 +15520,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -15550,7 +15549,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -15579,7 +15578,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -15608,7 +15607,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
@@ -15637,7 +15636,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -15666,7 +15665,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -15695,7 +15694,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
@@ -15724,7 +15723,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -15753,7 +15752,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
@@ -15782,7 +15781,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>59</v>
       </c>
@@ -15811,7 +15810,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>63</v>
       </c>
@@ -15840,7 +15839,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>63</v>
       </c>
@@ -15869,7 +15868,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>70</v>
       </c>
@@ -15898,7 +15897,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
@@ -15927,7 +15926,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>70</v>
       </c>
@@ -15956,7 +15955,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>70</v>
       </c>
@@ -15985,7 +15984,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>84</v>
       </c>
@@ -16014,7 +16013,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -16043,7 +16042,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>91</v>
       </c>
@@ -16072,7 +16071,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>95</v>
       </c>
@@ -16101,7 +16100,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>99</v>
       </c>
@@ -16130,7 +16129,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>99</v>
       </c>
@@ -16159,7 +16158,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>107</v>
       </c>
@@ -16188,7 +16187,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>107</v>
       </c>
@@ -16217,7 +16216,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>115</v>
       </c>
@@ -16246,7 +16245,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>119</v>
       </c>
@@ -16271,7 +16270,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>122</v>
       </c>
@@ -16300,7 +16299,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>126</v>
       </c>
@@ -16327,7 +16326,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>126</v>
       </c>
@@ -16352,7 +16351,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>130</v>
       </c>
@@ -16381,7 +16380,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="82.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>130</v>
       </c>
@@ -16410,7 +16409,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>138</v>
       </c>
@@ -16439,7 +16438,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>138</v>
       </c>
@@ -16466,7 +16465,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>144</v>
       </c>
@@ -16495,7 +16494,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>144</v>
       </c>
@@ -16524,7 +16523,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>144</v>
       </c>
@@ -16553,7 +16552,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>156</v>
       </c>
@@ -16582,7 +16581,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="69" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>161</v>
       </c>
@@ -16611,7 +16610,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>46</v>
       </c>
@@ -16640,7 +16639,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>119</v>
       </c>
@@ -16665,7 +16664,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="110.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>122</v>
       </c>
@@ -16692,7 +16691,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>144</v>
       </c>
@@ -16717,7 +16716,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>156</v>
       </c>
@@ -16743,13 +16742,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I48" xr:uid="{2E8EE7F9-C83B-46E0-BD66-45A599C1C12A}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="GESTIÓN JURÍDICA Y NORMATIVA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <conditionalFormatting sqref="H3">
     <cfRule type="duplicateValues" dxfId="15" priority="12"/>
   </conditionalFormatting>
